--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -423,13 +423,70 @@
     </r>
   </si>
   <si>
-    <t>Bồ Đào Nha - Congo</t>
-  </si>
-  <si>
-    <t>Anh - Croatia</t>
-  </si>
-  <si>
-    <t>Ghana - Panama</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Bồ Đào Nha</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Congo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Anh</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Croatia</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Ghana</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Panama</t>
+    </r>
   </si>
   <si>
     <t>Colombia - Uzbekistan</t>
@@ -448,6 +505,9 @@
   </si>
   <si>
     <t>SUM</t>
+  </si>
+  <si>
+    <t>AVG</t>
   </si>
 </sst>
 </file>
@@ -795,91 +855,91 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2">
@@ -1793,36 +1853,174 @@
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
+      <c r="C23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="E23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="G23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="I23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="K23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="M23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="N23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="O23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="S23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V23" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="W23" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X23" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
+      <c r="B24" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D24" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J24" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="K24" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L24" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="M24" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P24" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T24" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U24" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V24" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="W24" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X24" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
+      <c r="B25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="C25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="E25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="H25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="I25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="K25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="N25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="S25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U25" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V25" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X25" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
         <v>46</v>
       </c>
+      <c r="G26" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X26" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -2432,7 +2630,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="7">
-        <v>240.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="3">
@@ -2440,39 +2638,39 @@
         <v>10</v>
       </c>
       <c r="B3" s="7">
-        <v>240.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B4" s="7">
-        <v>220.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B5" s="7">
-        <v>220.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B6" s="7">
-        <v>220.0</v>
+        <v>260.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>220.0</v>
+        <v>260.0</v>
       </c>
     </row>
     <row r="8">
@@ -2480,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="7">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="9">
@@ -2488,55 +2686,55 @@
         <v>3</v>
       </c>
       <c r="B9" s="7">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="7">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B11" s="7">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B12" s="7">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B13" s="7">
-        <v>200.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B14" s="7">
-        <v>200.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B15" s="7">
-        <v>180.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="16">
@@ -2544,15 +2742,15 @@
         <v>11</v>
       </c>
       <c r="B16" s="7">
-        <v>180.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="7">
-        <v>180.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="18">
@@ -2560,31 +2758,31 @@
         <v>15</v>
       </c>
       <c r="B18" s="7">
-        <v>180.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="7">
-        <v>180.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B20" s="7">
-        <v>180.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B21" s="7">
-        <v>160.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="22">
@@ -2592,7 +2790,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="7">
-        <v>160.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="23">
@@ -2600,7 +2798,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="7">
-        <v>100.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="24">
@@ -2612,11 +2810,17 @@
       </c>
       <c r="B25" s="13">
         <f>SUM(B2:B23)</f>
-        <v>4260</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10"/>
+      <c r="A26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="13">
+        <f>ROUND(B25/22,0)</f>
+        <v>235</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -489,7 +489,21 @@
     </r>
   </si>
   <si>
-    <t>Colombia - Uzbekistan</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Colombia</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Uzbekistan</t>
+    </r>
   </si>
   <si>
     <t>Séc - Nam Phi</t>
@@ -855,7 +869,7 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
@@ -863,7 +877,7 @@
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
@@ -879,15 +893,15 @@
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
@@ -911,7 +925,7 @@
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
@@ -919,23 +933,23 @@
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
@@ -2015,12 +2029,45 @@
       <c r="A26" s="5" t="s">
         <v>46</v>
       </c>
+      <c r="B26" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D26" s="6">
+        <v>20.0</v>
+      </c>
       <c r="G26" s="6">
         <v>20.0</v>
       </c>
+      <c r="H26" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="I26" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J26" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P26" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R26" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="S26" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T26" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U26" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V26" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X26" s="7">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27">
@@ -2627,23 +2674,23 @@
 2,
 FALSE
 )</f>
-        <v>Tiến Tùng</v>
+        <v>Chính Đạt</v>
       </c>
       <c r="B2" s="7">
-        <v>280.0</v>
+        <v>300.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B3" s="7">
-        <v>280.0</v>
+        <v>300.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B4" s="7">
         <v>280.0</v>
@@ -2651,7 +2698,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B5" s="7">
         <v>280.0</v>
@@ -2659,7 +2706,7 @@
     </row>
     <row r="6">
       <c r="A6" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="7">
         <v>260.0</v>
@@ -2667,7 +2714,7 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B7" s="7">
         <v>260.0</v>
@@ -2675,31 +2722,31 @@
     </row>
     <row r="8">
       <c r="A8" s="10" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B8" s="7">
-        <v>240.0</v>
+        <v>260.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>240.0</v>
+        <v>260.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B10" s="7">
-        <v>240.0</v>
+        <v>260.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B11" s="7">
         <v>240.0</v>
@@ -2707,7 +2754,7 @@
     </row>
     <row r="12">
       <c r="A12" s="10" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B12" s="7">
         <v>240.0</v>
@@ -2715,39 +2762,39 @@
     </row>
     <row r="13">
       <c r="A13" s="10" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B13" s="7">
-        <v>220.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>220.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B15" s="7">
-        <v>220.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B16" s="7">
-        <v>220.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B17" s="7">
         <v>220.0</v>
@@ -2755,7 +2802,7 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B18" s="7">
         <v>220.0</v>
@@ -2763,7 +2810,7 @@
     </row>
     <row r="19">
       <c r="A19" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B19" s="7">
         <v>220.0</v>
@@ -2771,7 +2818,7 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B20" s="7">
         <v>220.0</v>
@@ -2779,7 +2826,7 @@
     </row>
     <row r="21">
       <c r="A21" s="10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B21" s="7">
         <v>220.0</v>
@@ -2787,10 +2834,10 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B22" s="7">
-        <v>200.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="23">
@@ -2798,7 +2845,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="7">
-        <v>160.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="24">
@@ -2810,7 +2857,7 @@
       </c>
       <c r="B25" s="13">
         <f>SUM(B2:B23)</f>
-        <v>5180</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="26">
@@ -2819,7 +2866,7 @@
       </c>
       <c r="B26" s="13">
         <f>ROUND(B25/22,0)</f>
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -249,7 +249,7 @@
         <b/>
         <color theme="1"/>
       </rPr>
-      <t>Nhật</t>
+      <t>Nhật Bản</t>
     </r>
   </si>
   <si>
@@ -506,7 +506,197 @@
     </r>
   </si>
   <si>
-    <t>Séc - Nam Phi</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Séc - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Nam Phi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Thuỵ Sĩ</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Bosina</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Canada</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Qatar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Mexico</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Hàn Quốc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Mỹ</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Úc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Ma Rốc</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Scotland</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Brazil</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Halti</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Thổ Nhĩ Kì - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Paraguay</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Hà Lan</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Thuỵ Điển</t>
+    </r>
+  </si>
+  <si>
+    <t>Đức - Bờ Biển Ngà</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Ecuador - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Curacao</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Nhật Bản</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Tuynidi</t>
+    </r>
+  </si>
+  <si>
+    <t>Tây Ban Nha - Ả Rập Xê út</t>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -869,91 +1059,91 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>260</v>
+        <v>440</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>340</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>460</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>260</v>
+        <v>360</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>420</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>320</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>260</v>
+        <v>360</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2">
@@ -2074,90 +2264,465 @@
       <c r="A27" s="5" t="s">
         <v>47</v>
       </c>
+      <c r="C27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="E27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="G27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="H27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="I27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="N27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="O27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V27" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="W27" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X27" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8"/>
+      <c r="A28" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="G28" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="H28" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L28" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="M28" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T28" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U28" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V28" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X28" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8"/>
+      <c r="A29" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J29" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L29" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="M29" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P29" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R29" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="S29" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T29" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U29" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V29" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="W29" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X29" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8"/>
+      <c r="A30" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="C30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="E30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="G30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="H30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="M30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="S30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T30" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U30" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X30" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8"/>
+      <c r="A31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F31" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="H31" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="K31" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L31" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="W31" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X31" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8"/>
+      <c r="A32" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F32" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X32" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8"/>
+      <c r="A33" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F33" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="H33" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R33" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X33" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8"/>
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="I34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="K34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="M34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="N34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="O34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="S34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V34" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="W34" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X34" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8"/>
+      <c r="A35" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="C35" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F35" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T35" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X35" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8"/>
+      <c r="A36" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="C36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="E36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="G36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="H36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="I36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="K36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="M36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="N36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="O36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="S36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V36" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="W36" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X36" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8"/>
+      <c r="A37" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F37" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J37" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="M37" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="N37" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="O37" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="S37" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U37" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V37" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X37" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8"/>
+      <c r="A38" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="G38" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X38" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8"/>
+      <c r="A39" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="X39" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2658,13 +3223,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
@@ -2674,26 +3239,26 @@
 2,
 FALSE
 )</f>
-        <v>Chính Đạt</v>
+        <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="7">
-        <v>300.0</v>
+        <v>460.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B3" s="7">
-        <v>300.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B4" s="7">
-        <v>280.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="5">
@@ -2701,23 +3266,23 @@
         <v>10</v>
       </c>
       <c r="B5" s="7">
-        <v>280.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B6" s="7">
-        <v>260.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B7" s="7">
-        <v>260.0</v>
+        <v>380.0</v>
       </c>
     </row>
     <row r="8">
@@ -2725,15 +3290,15 @@
         <v>5</v>
       </c>
       <c r="B8" s="7">
-        <v>260.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="7">
-        <v>260.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="10">
@@ -2741,111 +3306,111 @@
         <v>14</v>
       </c>
       <c r="B10" s="7">
-        <v>260.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B11" s="7">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B12" s="7">
-        <v>240.0</v>
+        <v>340.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B13" s="7">
-        <v>240.0</v>
+        <v>340.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="7">
-        <v>240.0</v>
+        <v>340.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B15" s="7">
-        <v>240.0</v>
+        <v>320.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B16" s="7">
-        <v>240.0</v>
+        <v>320.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B17" s="7">
-        <v>220.0</v>
+        <v>320.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B18" s="7">
-        <v>220.0</v>
+        <v>320.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B19" s="7">
-        <v>220.0</v>
+        <v>300.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B20" s="7">
-        <v>220.0</v>
+        <v>300.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B21" s="7">
-        <v>220.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B22" s="7">
-        <v>220.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B23" s="7">
-        <v>180.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="24">
@@ -2853,20 +3418,20 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B25" s="13">
         <f>SUM(B2:B23)</f>
-        <v>5400</v>
+        <v>7740</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B26" s="13">
         <f>ROUND(B25/22,0)</f>
-        <v>245</v>
+        <v>352</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -696,7 +696,58 @@
     </r>
   </si>
   <si>
-    <t>Tây Ban Nha - Ả Rập Xê út</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Tây Ban Nha</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Ả Rập Xê út</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Bỉ - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Iran</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Uruguay - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Cape Varde</t>
+    </r>
+  </si>
+  <si>
+    <t>Ai Cập - New Zealand</t>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1059,7 +1110,7 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
@@ -1067,7 +1118,7 @@
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
@@ -1075,11 +1126,11 @@
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -1087,35 +1138,35 @@
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
@@ -1123,27 +1174,27 @@
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
@@ -2723,27 +2774,135 @@
       <c r="A39" s="5" t="s">
         <v>59</v>
       </c>
+      <c r="B39" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D39" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J39" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L39" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P39" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R39" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V39" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="W39" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X39" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8"/>
+      <c r="A40" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="G40" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="I40" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="K40" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="M40" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="N40" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="O40" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="S40" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T40" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U40" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V40" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="W40" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X40" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8"/>
+      <c r="A41" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="G41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="I41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="K41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="M41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="N41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="O41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="S41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T41" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="W41" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X41" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8"/>
+      <c r="A42" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="X42" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -3223,13 +3382,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2">
@@ -3242,7 +3401,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="7">
-        <v>460.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="3">
@@ -3250,23 +3409,23 @@
         <v>0</v>
       </c>
       <c r="B3" s="7">
-        <v>440.0</v>
+        <v>460.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B4" s="7">
-        <v>440.0</v>
+        <v>460.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B5" s="7">
-        <v>420.0</v>
+        <v>460.0</v>
       </c>
     </row>
     <row r="6">
@@ -3274,7 +3433,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="7">
-        <v>420.0</v>
+        <v>460.0</v>
       </c>
     </row>
     <row r="7">
@@ -3282,7 +3441,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="7">
-        <v>380.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="8">
@@ -3290,55 +3449,55 @@
         <v>5</v>
       </c>
       <c r="B8" s="7">
-        <v>360.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B9" s="7">
-        <v>360.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B10" s="7">
-        <v>360.0</v>
+        <v>380.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B11" s="7">
-        <v>360.0</v>
+        <v>380.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B12" s="7">
-        <v>340.0</v>
+        <v>380.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B13" s="7">
-        <v>340.0</v>
+        <v>380.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B14" s="7">
-        <v>340.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="15">
@@ -3346,7 +3505,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="7">
-        <v>320.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="16">
@@ -3354,7 +3513,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="7">
-        <v>320.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="17">
@@ -3362,47 +3521,47 @@
         <v>17</v>
       </c>
       <c r="B17" s="7">
-        <v>320.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B18" s="7">
-        <v>320.0</v>
+        <v>340.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B19" s="7">
-        <v>300.0</v>
+        <v>340.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B20" s="7">
-        <v>300.0</v>
+        <v>320.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B21" s="7">
-        <v>280.0</v>
+        <v>320.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B22" s="7">
-        <v>280.0</v>
+        <v>300.0</v>
       </c>
     </row>
     <row r="23">
@@ -3418,20 +3577,20 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B25" s="13">
         <f>SUM(B2:B23)</f>
-        <v>7740</v>
+        <v>8420</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B26" s="13">
         <f>ROUND(B25/22,0)</f>
-        <v>352</v>
+        <v>383</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -747,7 +747,33 @@
     </r>
   </si>
   <si>
-    <t>Ai Cập - New Zealand</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Ai Cập - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>New Zealand</t>
+    </r>
+  </si>
+  <si>
+    <t>Arrgentina - Áo</t>
+  </si>
+  <si>
+    <t>Pháp - Iraq</t>
+  </si>
+  <si>
+    <t>Na Uy - Senegal</t>
+  </si>
+  <si>
+    <t>Algerie - Jordan</t>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1130,7 +1156,7 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -1142,7 +1168,7 @@
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
@@ -1158,11 +1184,11 @@
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
@@ -1178,7 +1204,7 @@
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
@@ -1194,7 +1220,7 @@
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2">
@@ -2903,34 +2929,60 @@
       <c r="A42" s="5" t="s">
         <v>62</v>
       </c>
+      <c r="G42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="J42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="N42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="O42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="S42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="W42" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X42" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8"/>
+      <c r="A43" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="X43" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8"/>
+      <c r="A44" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="X44" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8"/>
+      <c r="A45" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="X45" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8"/>
+      <c r="A46" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="X46" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -3382,13 +3434,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2">
@@ -3438,7 +3490,7 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B7" s="7">
         <v>420.0</v>
@@ -3446,10 +3498,10 @@
     </row>
     <row r="8">
       <c r="A8" s="10" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B8" s="7">
-        <v>400.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="9">
@@ -3462,15 +3514,15 @@
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B10" s="7">
-        <v>380.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B11" s="7">
         <v>380.0</v>
@@ -3478,7 +3530,7 @@
     </row>
     <row r="12">
       <c r="A12" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7">
         <v>380.0</v>
@@ -3486,7 +3538,7 @@
     </row>
     <row r="13">
       <c r="A13" s="10" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7">
         <v>380.0</v>
@@ -3494,23 +3546,23 @@
     </row>
     <row r="14">
       <c r="A14" s="10" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B14" s="7">
-        <v>360.0</v>
+        <v>380.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B15" s="7">
-        <v>360.0</v>
+        <v>380.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B16" s="7">
         <v>360.0</v>
@@ -3518,7 +3570,7 @@
     </row>
     <row r="17">
       <c r="A17" s="10" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B17" s="7">
         <v>360.0</v>
@@ -3526,15 +3578,15 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B18" s="7">
-        <v>340.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B19" s="7">
         <v>340.0</v>
@@ -3545,7 +3597,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="7">
-        <v>320.0</v>
+        <v>340.0</v>
       </c>
     </row>
     <row r="21">
@@ -3577,20 +3629,20 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B25" s="13">
         <f>SUM(B2:B23)</f>
-        <v>8420</v>
+        <v>8540</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B26" s="13">
         <f>ROUND(B25/22,0)</f>
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -750,17 +750,17 @@
     <r>
       <rPr>
         <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">Ai Cập - </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>New Zealand</t>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Ai Cập</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - New Zealand</t>
     </r>
   </si>
   <si>
@@ -1136,91 +1136,91 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
@@ -2929,27 +2929,57 @@
       <c r="A42" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W42" s="6">
+      <c r="B42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="C42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="E42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="H42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="I42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="K42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="M42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="U42" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="V42" s="6">
         <v>20.0</v>
       </c>
       <c r="X42" s="7">
         <f t="shared" si="2"/>
-        <v>120</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43">
@@ -3453,7 +3483,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="7">
-        <v>500.0</v>
+        <v>520.0</v>
       </c>
     </row>
     <row r="3">
@@ -3461,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="7">
-        <v>460.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="4">
@@ -3469,7 +3499,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="7">
-        <v>460.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="5">
@@ -3477,7 +3507,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="7">
-        <v>460.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="6">
@@ -3485,20 +3515,20 @@
         <v>20</v>
       </c>
       <c r="B6" s="7">
-        <v>460.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B7" s="7">
-        <v>420.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="7">
         <v>420.0</v>
@@ -3506,7 +3536,7 @@
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B9" s="7">
         <v>400.0</v>
@@ -3514,7 +3544,7 @@
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B10" s="7">
         <v>400.0</v>
@@ -3522,23 +3552,23 @@
     </row>
     <row r="11">
       <c r="A11" s="10" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B11" s="7">
-        <v>380.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" s="7">
-        <v>380.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B13" s="7">
         <v>380.0</v>
@@ -3546,7 +3576,7 @@
     </row>
     <row r="14">
       <c r="A14" s="10" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B14" s="7">
         <v>380.0</v>
@@ -3554,7 +3584,7 @@
     </row>
     <row r="15">
       <c r="A15" s="10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B15" s="7">
         <v>380.0</v>
@@ -3562,7 +3592,7 @@
     </row>
     <row r="16">
       <c r="A16" s="10" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B16" s="7">
         <v>360.0</v>
@@ -3570,7 +3600,7 @@
     </row>
     <row r="17">
       <c r="A17" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B17" s="7">
         <v>360.0</v>
@@ -3578,7 +3608,7 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" s="7">
         <v>360.0</v>
@@ -3586,7 +3616,7 @@
     </row>
     <row r="19">
       <c r="A19" s="10" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B19" s="7">
         <v>340.0</v>
@@ -3594,7 +3624,7 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B20" s="7">
         <v>340.0</v>
@@ -3602,7 +3632,7 @@
     </row>
     <row r="21">
       <c r="A21" s="10" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B21" s="7">
         <v>320.0</v>
@@ -3610,10 +3640,10 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B22" s="7">
-        <v>300.0</v>
+        <v>320.0</v>
       </c>
     </row>
     <row r="23">
@@ -3621,7 +3651,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="7">
-        <v>280.0</v>
+        <v>300.0</v>
       </c>
     </row>
     <row r="24">
@@ -3633,7 +3663,7 @@
       </c>
       <c r="B25" s="13">
         <f>SUM(B2:B23)</f>
-        <v>8540</v>
+        <v>8740</v>
       </c>
     </row>
     <row r="26">
@@ -3642,7 +3672,7 @@
       </c>
       <c r="B26" s="13">
         <f>ROUND(B25/22,0)</f>
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -764,13 +764,51 @@
     </r>
   </si>
   <si>
-    <t>Arrgentina - Áo</t>
-  </si>
-  <si>
-    <t>Pháp - Iraq</t>
-  </si>
-  <si>
-    <t>Na Uy - Senegal</t>
+    <r>
+      <t>Arrgentina</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b val="0"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Áo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Pháp</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Iraq</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Na Uy</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Senegal</t>
+    </r>
   </si>
   <si>
     <t>Algerie - Jordan</t>
@@ -822,13 +860,13 @@
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="15.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -872,7 +910,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -895,8 +933,11 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -905,10 +946,10 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1136,11 +1177,11 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
@@ -1148,19 +1189,19 @@
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
@@ -1176,7 +1217,7 @@
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
@@ -1192,15 +1233,15 @@
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
@@ -1208,7 +1249,7 @@
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
@@ -2983,30 +3024,87 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="8" t="s">
         <v>63</v>
       </c>
+      <c r="B43" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="C43" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="E43" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="G43" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="H43" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L43" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="P43" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R43" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X43" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
         <v>64</v>
       </c>
+      <c r="B44" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X44" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
         <v>65</v>
       </c>
+      <c r="B45" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="C45" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="E45" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="F45" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="H45" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="L45" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="R45" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="T45" s="6">
+        <v>20.0</v>
+      </c>
       <c r="X45" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46">
@@ -3019,427 +3117,427 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8"/>
+      <c r="A47" s="9"/>
       <c r="X47" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8"/>
+      <c r="A48" s="9"/>
       <c r="X48" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8"/>
+      <c r="A49" s="9"/>
       <c r="X49" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8"/>
+      <c r="A50" s="9"/>
       <c r="X50" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8"/>
+      <c r="A51" s="9"/>
       <c r="X51" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8"/>
+      <c r="A52" s="9"/>
       <c r="X52" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8"/>
+      <c r="A53" s="9"/>
       <c r="X53" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8"/>
+      <c r="A54" s="9"/>
       <c r="X54" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8"/>
+      <c r="A55" s="9"/>
       <c r="X55" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8"/>
+      <c r="A56" s="9"/>
       <c r="X56" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8"/>
+      <c r="A57" s="9"/>
       <c r="X57" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8"/>
+      <c r="A58" s="9"/>
       <c r="X58" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8"/>
+      <c r="A59" s="9"/>
       <c r="X59" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8"/>
+      <c r="A60" s="9"/>
       <c r="X60" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8"/>
+      <c r="A61" s="9"/>
       <c r="X61" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8"/>
+      <c r="A62" s="9"/>
       <c r="X62" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8"/>
+      <c r="A63" s="9"/>
       <c r="X63" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8"/>
+      <c r="A64" s="9"/>
       <c r="X64" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8"/>
+      <c r="A65" s="9"/>
       <c r="X65" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8"/>
+      <c r="A66" s="9"/>
       <c r="X66" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8"/>
+      <c r="A67" s="9"/>
       <c r="X67" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8"/>
+      <c r="A68" s="9"/>
       <c r="X68" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8"/>
+      <c r="A69" s="9"/>
       <c r="X69" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8"/>
+      <c r="A70" s="9"/>
       <c r="X70" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8"/>
+      <c r="A71" s="9"/>
       <c r="X71" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8"/>
+      <c r="A72" s="9"/>
       <c r="X72" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8"/>
+      <c r="A73" s="9"/>
       <c r="X73" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8"/>
+      <c r="A74" s="9"/>
       <c r="X74" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8"/>
+      <c r="A75" s="9"/>
       <c r="X75" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8"/>
+      <c r="A76" s="9"/>
       <c r="X76" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8"/>
+      <c r="A77" s="9"/>
       <c r="X77" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8"/>
+      <c r="A78" s="9"/>
       <c r="X78" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8"/>
+      <c r="A79" s="9"/>
       <c r="X79" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8"/>
+      <c r="A80" s="9"/>
       <c r="X80" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8"/>
+      <c r="A81" s="9"/>
       <c r="X81" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8"/>
+      <c r="A82" s="9"/>
       <c r="X82" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8"/>
+      <c r="A83" s="9"/>
       <c r="X83" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8"/>
+      <c r="A84" s="9"/>
       <c r="X84" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8"/>
+      <c r="A85" s="9"/>
       <c r="X85" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8"/>
+      <c r="A86" s="9"/>
       <c r="X86" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8"/>
+      <c r="A87" s="9"/>
       <c r="X87" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8"/>
+      <c r="A88" s="9"/>
       <c r="X88" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8"/>
+      <c r="A89" s="9"/>
       <c r="X89" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8"/>
+      <c r="A90" s="9"/>
       <c r="X90" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8"/>
+      <c r="A91" s="9"/>
       <c r="X91" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8"/>
+      <c r="A92" s="9"/>
       <c r="X92" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8"/>
+      <c r="A93" s="9"/>
       <c r="X93" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8"/>
+      <c r="A94" s="9"/>
       <c r="X94" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="8"/>
+      <c r="A95" s="9"/>
       <c r="X95" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="8"/>
+      <c r="A96" s="9"/>
       <c r="X96" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="8"/>
+      <c r="A97" s="9"/>
       <c r="X97" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8"/>
+      <c r="A98" s="9"/>
       <c r="X98" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8"/>
+      <c r="A99" s="9"/>
       <c r="X99" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8"/>
+      <c r="A100" s="9"/>
       <c r="X100" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8"/>
+      <c r="A101" s="9"/>
       <c r="X101" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8"/>
+      <c r="A102" s="9"/>
       <c r="X102" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="8"/>
+      <c r="A103" s="9"/>
       <c r="X103" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="8"/>
+      <c r="A104" s="9"/>
       <c r="X104" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8"/>
+      <c r="A105" s="9"/>
       <c r="X105" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8"/>
+      <c r="A106" s="9"/>
       <c r="X106" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="8"/>
+      <c r="A107" s="9"/>
       <c r="X107" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -3463,47 +3561,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="str">
+      <c r="A2" s="11" t="str">
         <f t="array" ref="A2:B23">SORT(
 TRANSPOSE({Detail!B2:W2;Detail!B1:W1}),
 2,
 FALSE
 )</f>
-        <v>Tiến Tùng</v>
+        <v>Thái Bình</v>
       </c>
       <c r="B2" s="7">
+        <v>540.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="7">
+        <v>540.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="7">
         <v>520.0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="7">
-        <v>480.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="7">
-        <v>480.0</v>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="7">
@@ -3511,7 +3609,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="7">
@@ -3519,173 +3617,173 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="7">
+        <v>460.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="7">
-        <v>440.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="s">
-        <v>16</v>
-      </c>
       <c r="B8" s="7">
+        <v>460.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7">
         <v>420.0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>400.0</v>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="10" t="s">
-        <v>5</v>
+      <c r="A10" s="11" t="s">
+        <v>6</v>
       </c>
       <c r="B10" s="7">
-        <v>400.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="s">
-        <v>11</v>
+      <c r="A11" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="B11" s="7">
-        <v>400.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="s">
-        <v>14</v>
+      <c r="A12" s="11" t="s">
+        <v>1</v>
       </c>
       <c r="B12" s="7">
         <v>400.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="s">
-        <v>6</v>
+      <c r="A13" s="11" t="s">
+        <v>2</v>
       </c>
       <c r="B13" s="7">
-        <v>380.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7">
+        <v>400.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="s">
         <v>7</v>
-      </c>
-      <c r="B14" s="7">
-        <v>380.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="s">
-        <v>21</v>
       </c>
       <c r="B15" s="7">
         <v>380.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="s">
-        <v>1</v>
+      <c r="A16" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="B16" s="7">
-        <v>360.0</v>
+        <v>380.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="s">
-        <v>12</v>
+      <c r="A17" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="B17" s="7">
         <v>360.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="s">
-        <v>17</v>
+      <c r="A18" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="B18" s="7">
         <v>360.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7">
+        <v>360.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="B19" s="7">
-        <v>340.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="s">
-        <v>13</v>
       </c>
       <c r="B20" s="7">
         <v>340.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="s">
-        <v>3</v>
+      <c r="A21" s="11" t="s">
+        <v>13</v>
       </c>
       <c r="B21" s="7">
+        <v>340.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="7">
+        <v>340.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="7">
         <v>320.0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="7">
-        <v>320.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="7">
-        <v>300.0</v>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="11"/>
+      <c r="A24" s="12"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="14">
         <f>SUM(B2:B23)</f>
-        <v>8740</v>
+        <v>9120</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="14">
         <f>ROUND(B25/22,0)</f>
-        <v>397</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10"/>
+      <c r="A27" s="11"/>
     </row>
     <row r="28">
-      <c r="A28" s="10"/>
+      <c r="A28" s="11"/>
     </row>
     <row r="29">
-      <c r="A29" s="10"/>
+      <c r="A29" s="11"/>
     </row>
     <row r="30">
-      <c r="A30" s="10"/>
+      <c r="A30" s="11"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="74">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -811,7 +811,21 @@
     </r>
   </si>
   <si>
-    <t>Algerie - Jordan</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Algerie - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Jordan</t>
+    </r>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -826,7 +840,13 @@
     <t>SUM</t>
   </si>
   <si>
-    <t>AVG</t>
+    <t>AVG/người</t>
+  </si>
+  <si>
+    <t>AVG/trận</t>
+  </si>
+  <si>
+    <t>XS WIN 50%</t>
   </si>
 </sst>
 </file>
@@ -910,13 +930,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -932,7 +953,6 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -950,6 +970,9 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1181,15 +1204,15 @@
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
@@ -1201,43 +1224,43 @@
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
@@ -1245,1780 +1268,1784 @@
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>400</v>
+      </c>
+      <c r="X1" s="2">
+        <f>COUNTIF(X3:X130,"&gt;0")</f>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="S2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="V2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C3" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H3" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L3" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P3" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R3" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S3" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U3" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W3" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X3" s="7">
+      <c r="B3" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C3" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I3" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L3" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P3" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R3" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S3" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U3" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W3" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X3" s="2">
         <f t="shared" ref="X3:X107" si="2">sum(B3:W3)</f>
         <v>220</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E4" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F4" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G4" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M4" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U4" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X4" s="7">
+      <c r="B4" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E4" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F4" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I4" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M4" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U4" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X4" s="2">
         <f t="shared" si="2"/>
         <v>140</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V5" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X5" s="7">
+      <c r="C5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X5" s="2">
         <f t="shared" si="2"/>
         <v>260</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D6" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H6" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L6" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M6" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O6" s="6"/>
-      <c r="S6" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T6" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U6" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V6" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X6" s="7">
+      <c r="B6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="S6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X6" s="2">
         <f t="shared" si="2"/>
         <v>220</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W7" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X7" s="7">
+      <c r="C7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X7" s="2">
         <f t="shared" si="2"/>
         <v>280</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W8" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X8" s="7">
+      <c r="C8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W8" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X8" s="2">
         <f t="shared" si="2"/>
         <v>420</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M9" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X9" s="7">
+      <c r="B9" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M9" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X9" s="2">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X10" s="7">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X10" s="2">
         <f t="shared" si="2"/>
         <v>260</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X11" s="7">
+      <c r="B11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W11" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X11" s="2">
         <f t="shared" si="2"/>
         <v>300</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F12" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G12" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L12" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N12" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O12" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X12" s="7">
+      <c r="E12" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F12" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L12" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N12" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O12" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X12" s="2">
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F13" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M13" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N13" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O13" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U13" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W13" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X13" s="7">
+      <c r="E13" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F13" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M13" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N13" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O13" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U13" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W13" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X13" s="2">
         <f t="shared" si="2"/>
         <v>140</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X14" s="7">
+      <c r="B14" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X14" s="2">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W15" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X15" s="7">
+      <c r="C15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W15" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X15" s="2">
         <f t="shared" si="2"/>
         <v>380</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U16" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X16" s="7">
+      <c r="C16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U16" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X16" s="2">
         <f t="shared" si="2"/>
         <v>320</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G17" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H17" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K17" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M17" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N17" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O17" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X17" s="7">
+      <c r="F17" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H17" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K17" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M17" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N17" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O17" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X17" s="2">
         <f t="shared" si="2"/>
         <v>140</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W18" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X18" s="7">
+      <c r="C18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W18" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X18" s="2">
         <f t="shared" si="2"/>
         <v>360</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V19" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X19" s="7">
+      <c r="B19" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V19" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X19" s="2">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D20" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L20" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M20" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T20" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V20" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X20" s="7">
+      <c r="B20" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D20" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L20" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M20" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T20" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V20" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X20" s="2">
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C21" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E21" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G21" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I21" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L21" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q21" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T21" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V21" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X21" s="7">
+      <c r="B21" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C21" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E21" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G21" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I21" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L21" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T21" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V21" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X21" s="2">
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W22" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X22" s="7">
+      <c r="B22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W22" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X22" s="2">
         <f t="shared" si="2"/>
         <v>280</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W23" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X23" s="7">
+      <c r="C23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W23" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X23" s="2">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D24" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J24" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K24" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L24" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M24" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P24" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T24" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U24" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V24" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W24" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X24" s="7">
+      <c r="B24" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D24" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J24" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K24" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L24" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M24" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P24" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T24" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U24" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V24" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W24" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X24" s="2">
         <f t="shared" si="2"/>
         <v>220</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V25" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X25" s="7">
+      <c r="B25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V25" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X25" s="2">
         <f t="shared" si="2"/>
         <v>280</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V26" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X26" s="7">
+      <c r="B26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V26" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X26" s="2">
         <f t="shared" si="2"/>
         <v>240</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W27" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X27" s="7">
+      <c r="C27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W27" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X27" s="2">
         <f t="shared" si="2"/>
         <v>340</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G28" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H28" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L28" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M28" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T28" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U28" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V28" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X28" s="7">
+      <c r="B28" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G28" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H28" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L28" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M28" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T28" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U28" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V28" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X28" s="2">
         <f t="shared" si="2"/>
         <v>160</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W29" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X29" s="7">
+      <c r="B29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W29" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X29" s="2">
         <f t="shared" si="2"/>
         <v>240</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U30" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X30" s="7">
+      <c r="B30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U30" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X30" s="2">
         <f t="shared" si="2"/>
         <v>300</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F31" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H31" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K31" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L31" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W31" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X31" s="7">
+      <c r="B31" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F31" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H31" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K31" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L31" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W31" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X31" s="2">
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F32" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X32" s="7">
+      <c r="B32" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F32" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X32" s="2">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F33" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H33" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R33" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X33" s="7">
+      <c r="B33" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F33" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H33" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R33" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X33" s="2">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W34" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X34" s="7">
+      <c r="D34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W34" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X34" s="2">
         <f t="shared" si="2"/>
         <v>320</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C35" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F35" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T35" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X35" s="7">
+      <c r="B35" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C35" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F35" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T35" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X35" s="2">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W36" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X36" s="7">
+      <c r="B36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W36" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X36" s="2">
         <f t="shared" si="2"/>
         <v>440</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F37" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J37" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M37" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N37" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O37" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S37" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U37" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V37" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X37" s="7">
+      <c r="D37" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F37" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J37" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M37" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N37" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O37" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S37" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U37" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V37" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X37" s="2">
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G38" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X38" s="7">
+      <c r="B38" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G38" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X38" s="2">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D39" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J39" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L39" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P39" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R39" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V39" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W39" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X39" s="7">
+      <c r="B39" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D39" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J39" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L39" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P39" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R39" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V39" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W39" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X39" s="2">
         <f t="shared" si="2"/>
         <v>160</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W40" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X40" s="7">
+      <c r="F40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W40" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X40" s="2">
         <f t="shared" si="2"/>
         <v>240</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="J41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="N41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="O41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="S41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="W41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X41" s="7">
+      <c r="D41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W41" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X41" s="2">
         <f t="shared" si="2"/>
         <v>280</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="I42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="K42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="M42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="U42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="V42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X42" s="7">
+      <c r="B42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V42" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X42" s="2">
         <f t="shared" si="2"/>
         <v>320</v>
       </c>
@@ -3027,518 +3054,572 @@
       <c r="A43" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B43" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C43" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E43" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="G43" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H43" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L43" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="P43" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q43" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R43" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X43" s="7">
+      <c r="B43" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C43" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E43" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G43" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H43" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L43" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P43" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R43" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X43" s="2">
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B44" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X44" s="7">
+      <c r="B44" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X44" s="2">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C45" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="E45" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="F45" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="H45" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="L45" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="Q45" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="R45" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="T45" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="X45" s="7">
+      <c r="B45" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C45" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E45" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F45" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H45" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L45" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q45" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R45" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T45" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X45" s="2">
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="X46" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="C46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X46" s="2">
+        <f t="shared" si="2"/>
+        <v>360</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9"/>
-      <c r="X47" s="7">
+      <c r="X47" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9"/>
-      <c r="X48" s="7">
+      <c r="X48" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9"/>
-      <c r="X49" s="7">
+      <c r="X49" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9"/>
-      <c r="X50" s="7">
+      <c r="X50" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9"/>
-      <c r="X51" s="7">
+      <c r="X51" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9"/>
-      <c r="X52" s="7">
+      <c r="X52" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9"/>
-      <c r="X53" s="7">
+      <c r="X53" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9"/>
-      <c r="X54" s="7">
+      <c r="X54" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9"/>
-      <c r="X55" s="7">
+      <c r="X55" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9"/>
-      <c r="X56" s="7">
+      <c r="X56" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9"/>
-      <c r="X57" s="7">
+      <c r="X57" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9"/>
-      <c r="X58" s="7">
+      <c r="X58" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9"/>
-      <c r="X59" s="7">
+      <c r="X59" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9"/>
-      <c r="X60" s="7">
+      <c r="X60" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9"/>
-      <c r="X61" s="7">
+      <c r="X61" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9"/>
-      <c r="X62" s="7">
+      <c r="X62" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9"/>
-      <c r="X63" s="7">
+      <c r="X63" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="9"/>
-      <c r="X64" s="7">
+      <c r="X64" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9"/>
-      <c r="X65" s="7">
+      <c r="X65" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9"/>
-      <c r="X66" s="7">
+      <c r="X66" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9"/>
-      <c r="X67" s="7">
+      <c r="X67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="9"/>
-      <c r="X68" s="7">
+      <c r="X68" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="9"/>
-      <c r="X69" s="7">
+      <c r="X69" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="9"/>
-      <c r="X70" s="7">
+      <c r="X70" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="9"/>
-      <c r="X71" s="7">
+      <c r="X71" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="9"/>
-      <c r="X72" s="7">
+      <c r="X72" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="9"/>
-      <c r="X73" s="7">
+      <c r="X73" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="9"/>
-      <c r="X74" s="7">
+      <c r="X74" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="9"/>
-      <c r="X75" s="7">
+      <c r="X75" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="9"/>
-      <c r="X76" s="7">
+      <c r="X76" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="9"/>
-      <c r="X77" s="7">
+      <c r="X77" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="9"/>
-      <c r="X78" s="7">
+      <c r="X78" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="9"/>
-      <c r="X79" s="7">
+      <c r="X79" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="9"/>
-      <c r="X80" s="7">
+      <c r="X80" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="9"/>
-      <c r="X81" s="7">
+      <c r="X81" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="9"/>
-      <c r="X82" s="7">
+      <c r="X82" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="9"/>
-      <c r="X83" s="7">
+      <c r="X83" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="9"/>
-      <c r="X84" s="7">
+      <c r="X84" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="9"/>
-      <c r="X85" s="7">
+      <c r="X85" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="9"/>
-      <c r="X86" s="7">
+      <c r="X86" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="9"/>
-      <c r="X87" s="7">
+      <c r="X87" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="9"/>
-      <c r="X88" s="7">
+      <c r="X88" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="9"/>
-      <c r="X89" s="7">
+      <c r="X89" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="9"/>
-      <c r="X90" s="7">
+      <c r="X90" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="9"/>
-      <c r="X91" s="7">
+      <c r="X91" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="9"/>
-      <c r="X92" s="7">
+      <c r="X92" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="9"/>
-      <c r="X93" s="7">
+      <c r="X93" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="9"/>
-      <c r="X94" s="7">
+      <c r="X94" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="9"/>
-      <c r="X95" s="7">
+      <c r="X95" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="9"/>
-      <c r="X96" s="7">
+      <c r="X96" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="9"/>
-      <c r="X97" s="7">
+      <c r="X97" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="9"/>
-      <c r="X98" s="7">
+      <c r="X98" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="9"/>
-      <c r="X99" s="7">
+      <c r="X99" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="9"/>
-      <c r="X100" s="7">
+      <c r="X100" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="9"/>
-      <c r="X101" s="7">
+      <c r="X101" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="9"/>
-      <c r="X102" s="7">
+      <c r="X102" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="9"/>
-      <c r="X103" s="7">
+      <c r="X103" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="9"/>
-      <c r="X104" s="7">
+      <c r="X104" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="9"/>
-      <c r="X105" s="7">
+      <c r="X105" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="9"/>
-      <c r="X106" s="7">
+      <c r="X106" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="9"/>
-      <c r="X107" s="7">
+      <c r="X107" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3580,7 +3661,7 @@
 )</f>
         <v>Thái Bình</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="2">
         <v>540.0</v>
       </c>
     </row>
@@ -3588,7 +3669,7 @@
       <c r="A3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="2">
         <v>540.0</v>
       </c>
     </row>
@@ -3596,160 +3677,160 @@
       <c r="A4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="7">
-        <v>520.0</v>
+      <c r="B4" s="2">
+        <v>540.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
-        <v>480.0</v>
+      <c r="B5" s="2">
+        <v>500.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="7">
-        <v>480.0</v>
+      <c r="B6" s="2">
+        <v>500.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="7">
-        <v>460.0</v>
+        <v>18</v>
+      </c>
+      <c r="B7" s="2">
+        <v>480.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="7">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2">
         <v>460.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="7">
-        <v>420.0</v>
+        <v>6</v>
+      </c>
+      <c r="B9" s="2">
+        <v>440.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7">
-        <v>420.0</v>
+        <v>14</v>
+      </c>
+      <c r="B10" s="2">
+        <v>440.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="7">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2">
         <v>420.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="7">
-        <v>400.0</v>
+        <v>2</v>
+      </c>
+      <c r="B12" s="2">
+        <v>420.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="7">
-        <v>400.0</v>
+        <v>5</v>
+      </c>
+      <c r="B13" s="2">
+        <v>420.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="7">
-        <v>400.0</v>
+      <c r="B14" s="2">
+        <v>420.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="7">
-        <v>380.0</v>
+      <c r="B15" s="2">
+        <v>400.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="7">
-        <v>380.0</v>
+      <c r="B16" s="2">
+        <v>400.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="7">
-        <v>360.0</v>
+      <c r="B17" s="2">
+        <v>380.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="7">
-        <v>360.0</v>
+      <c r="B18" s="2">
+        <v>380.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="7">
-        <v>360.0</v>
+      <c r="B19" s="2">
+        <v>380.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7">
-        <v>340.0</v>
+      <c r="B20" s="2">
+        <v>360.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="7">
-        <v>340.0</v>
+      <c r="B21" s="2">
+        <v>360.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="7">
-        <v>340.0</v>
+      <c r="B22" s="2">
+        <v>360.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="7">
-        <v>320.0</v>
+      <c r="B23" s="2">
+        <v>340.0</v>
       </c>
     </row>
     <row r="24">
@@ -3761,7 +3842,7 @@
       </c>
       <c r="B25" s="14">
         <f>SUM(B2:B23)</f>
-        <v>9120</v>
+        <v>9480</v>
       </c>
     </row>
     <row r="26">
@@ -3770,14 +3851,26 @@
       </c>
       <c r="B26" s="14">
         <f>ROUND(B25/22,0)</f>
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11"/>
+      <c r="A27" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="15">
+        <f>Round(B25/(Detail!X1),0)</f>
+        <v>215</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="11"/>
+      <c r="A28" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="14">
+        <f>(Detail!X1) * 10</f>
+        <v>440</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -1200,7 +1200,7 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
@@ -1216,11 +1216,11 @@
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
@@ -3138,6 +3138,9 @@
       <c r="A46" s="6" t="s">
         <v>66</v>
       </c>
+      <c r="B46" s="7">
+        <v>20.0</v>
+      </c>
       <c r="C46" s="7">
         <v>20.0</v>
       </c>
@@ -3147,6 +3150,12 @@
       <c r="E46" s="7">
         <v>20.0</v>
       </c>
+      <c r="F46" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G46" s="7">
+        <v>20.0</v>
+      </c>
       <c r="H46" s="7">
         <v>20.0</v>
       </c>
@@ -3177,6 +3186,9 @@
       <c r="Q46" s="7">
         <v>20.0</v>
       </c>
+      <c r="R46" s="7">
+        <v>20.0</v>
+      </c>
       <c r="S46" s="7">
         <v>20.0</v>
       </c>
@@ -3194,7 +3206,7 @@
       </c>
       <c r="X46" s="2">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>440</v>
       </c>
     </row>
     <row r="47">
@@ -3662,7 +3674,7 @@
         <v>Thái Bình</v>
       </c>
       <c r="B2" s="2">
-        <v>540.0</v>
+        <v>560.0</v>
       </c>
     </row>
     <row r="3">
@@ -3670,7 +3682,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>540.0</v>
+        <v>560.0</v>
       </c>
     </row>
     <row r="4">
@@ -3699,7 +3711,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2">
         <v>480.0</v>
@@ -3707,15 +3719,15 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2">
-        <v>460.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2">
         <v>440.0</v>
@@ -3723,7 +3735,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2">
         <v>440.0</v>
@@ -3731,15 +3743,15 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2">
-        <v>420.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="2">
         <v>420.0</v>
@@ -3747,7 +3759,7 @@
     </row>
     <row r="13">
       <c r="A13" s="11" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B13" s="2">
         <v>420.0</v>
@@ -3842,7 +3854,7 @@
       </c>
       <c r="B25" s="14">
         <f>SUM(B2:B23)</f>
-        <v>9480</v>
+        <v>9560</v>
       </c>
     </row>
     <row r="26">
@@ -3851,7 +3863,7 @@
       </c>
       <c r="B26" s="14">
         <f>ROUND(B25/22,0)</f>
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27">
@@ -3860,7 +3872,7 @@
       </c>
       <c r="B27" s="15">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="78">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -826,6 +826,60 @@
       </rPr>
       <t>Jordan</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Bồ Đào Nha</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Uzbekistan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Anh-  </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Ghana</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Croatia - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Panama</t>
+    </r>
+  </si>
+  <si>
+    <t>Colombia - Congo</t>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1200,31 +1254,31 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
@@ -1232,63 +1286,63 @@
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
@@ -3210,28 +3264,159 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9"/>
+      <c r="A47" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F47" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J47" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M47" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N47" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O47" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U47" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V47" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W47" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X47" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9"/>
+      <c r="A48" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T48" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W48" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X48" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9"/>
+      <c r="A49" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V49" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W49" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X49" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9"/>
+      <c r="A50" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="X50" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -3655,13 +3840,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
@@ -3671,18 +3856,18 @@
 2,
 FALSE
 )</f>
-        <v>Thái Bình</v>
+        <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>560.0</v>
+        <v>600.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>560.0</v>
+        <v>580.0</v>
       </c>
     </row>
     <row r="4">
@@ -3690,39 +3875,39 @@
         <v>10</v>
       </c>
       <c r="B4" s="2">
-        <v>540.0</v>
+        <v>580.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2">
-        <v>500.0</v>
+        <v>540.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2">
-        <v>500.0</v>
+        <v>520.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2">
-        <v>480.0</v>
+        <v>520.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2">
-        <v>480.0</v>
+        <v>520.0</v>
       </c>
     </row>
     <row r="9">
@@ -3730,15 +3915,15 @@
         <v>5</v>
       </c>
       <c r="B9" s="2">
-        <v>440.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>440.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="11">
@@ -3746,103 +3931,103 @@
         <v>14</v>
       </c>
       <c r="B11" s="2">
-        <v>440.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" s="2">
-        <v>420.0</v>
+        <v>460.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2">
-        <v>420.0</v>
+        <v>460.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2">
-        <v>420.0</v>
+        <v>460.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>400.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2">
-        <v>400.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2">
-        <v>380.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>380.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B19" s="2">
-        <v>380.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2">
-        <v>360.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2">
-        <v>360.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2">
-        <v>360.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B23" s="2">
-        <v>340.0</v>
+        <v>380.0</v>
       </c>
     </row>
     <row r="24">
@@ -3850,38 +4035,38 @@
     </row>
     <row r="25">
       <c r="A25" s="13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B25" s="14">
         <f>SUM(B2:B23)</f>
-        <v>9560</v>
+        <v>10380</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B26" s="14">
         <f>ROUND(B25/22,0)</f>
-        <v>435</v>
+        <v>472</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B27" s="15">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B28" s="14">
         <f>(Detail!X1) * 10</f>
-        <v>440</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -879,7 +879,21 @@
     </r>
   </si>
   <si>
-    <t>Colombia - Congo</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Colombia - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Congo</t>
+    </r>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1262,7 +1276,7 @@
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
@@ -1270,11 +1284,11 @@
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -1290,27 +1304,27 @@
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
@@ -1322,7 +1336,7 @@
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
@@ -1338,11 +1352,11 @@
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -3417,9 +3431,42 @@
       <c r="A50" s="6" t="s">
         <v>70</v>
       </c>
+      <c r="D50" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F50" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G50" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K50" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L50" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M50" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N50" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O50" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P50" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S50" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W50" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X50" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51">
@@ -3859,20 +3906,20 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>600.0</v>
+        <v>620.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>580.0</v>
+        <v>600.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B4" s="2">
         <v>580.0</v>
@@ -3915,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2">
-        <v>480.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="10">
@@ -3923,7 +3970,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>480.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="11">
@@ -3931,7 +3978,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="2">
-        <v>480.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="12">
@@ -3939,20 +3986,20 @@
         <v>2</v>
       </c>
       <c r="B12" s="2">
-        <v>460.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2">
-        <v>460.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B14" s="2">
         <v>460.0</v>
@@ -3960,15 +4007,15 @@
     </row>
     <row r="15">
       <c r="A15" s="11" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2">
-        <v>440.0</v>
+        <v>460.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B16" s="2">
         <v>440.0</v>
@@ -3979,7 +4026,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="2">
-        <v>420.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="18">
@@ -3987,20 +4034,20 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>420.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2">
-        <v>400.0</v>
+        <v>420.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B20" s="2">
         <v>400.0</v>
@@ -4008,7 +4055,7 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="2">
         <v>400.0</v>
@@ -4016,7 +4063,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="2">
         <v>400.0</v>
@@ -4039,7 +4086,7 @@
       </c>
       <c r="B25" s="14">
         <f>SUM(B2:B23)</f>
-        <v>10380</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="26">
@@ -4048,7 +4095,7 @@
       </c>
       <c r="B26" s="14">
         <f>ROUND(B25/22,0)</f>
-        <v>472</v>
+        <v>482</v>
       </c>
     </row>
     <row r="27">
@@ -4066,7 +4113,7 @@
       </c>
       <c r="B28" s="14">
         <f>(Detail!X1) * 10</f>
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="29">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="82">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -893,6 +893,60 @@
         <color theme="1"/>
       </rPr>
       <t>Congo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Thuỵ Sĩ </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>- Canada</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Bosnia</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>-Quatar</t>
+    </r>
+  </si>
+  <si>
+    <t>Ma rốc - Haiti</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Brazil</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>-Scotland</t>
     </r>
   </si>
   <si>
@@ -998,7 +1052,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1022,6 +1076,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1268,95 +1325,95 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>580</v>
+        <v>660</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>680</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>540</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
@@ -3470,399 +3527,566 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9"/>
+      <c r="A51" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V51" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W51" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X51" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9"/>
+      <c r="A52" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C52" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D52" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E52" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F52" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H52" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K52" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L52" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q52" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T52" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X52" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9"/>
+      <c r="A53" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V53" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W53" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X53" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9"/>
+      <c r="A54" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F54" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H54" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T54" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W54" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X54" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9"/>
+      <c r="A55" s="10"/>
       <c r="X55" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9"/>
+      <c r="A56" s="10"/>
       <c r="X56" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9"/>
+      <c r="A57" s="10"/>
       <c r="X57" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9"/>
+      <c r="A58" s="10"/>
       <c r="X58" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9"/>
+      <c r="A59" s="10"/>
       <c r="X59" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9"/>
+      <c r="A60" s="10"/>
       <c r="X60" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9"/>
+      <c r="A61" s="10"/>
       <c r="X61" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9"/>
+      <c r="A62" s="10"/>
       <c r="X62" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9"/>
+      <c r="A63" s="10"/>
       <c r="X63" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9"/>
+      <c r="A64" s="10"/>
       <c r="X64" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9"/>
+      <c r="A65" s="10"/>
       <c r="X65" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9"/>
+      <c r="A66" s="10"/>
       <c r="X66" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9"/>
+      <c r="A67" s="10"/>
       <c r="X67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9"/>
+      <c r="A68" s="10"/>
       <c r="X68" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9"/>
+      <c r="A69" s="10"/>
       <c r="X69" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9"/>
+      <c r="A70" s="10"/>
       <c r="X70" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9"/>
+      <c r="A71" s="10"/>
       <c r="X71" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9"/>
+      <c r="A72" s="10"/>
       <c r="X72" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9"/>
+      <c r="A73" s="10"/>
       <c r="X73" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="9"/>
+      <c r="A74" s="10"/>
       <c r="X74" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9"/>
+      <c r="A75" s="10"/>
       <c r="X75" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9"/>
+      <c r="A76" s="10"/>
       <c r="X76" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9"/>
+      <c r="A77" s="10"/>
       <c r="X77" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9"/>
+      <c r="A78" s="10"/>
       <c r="X78" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9"/>
+      <c r="A79" s="10"/>
       <c r="X79" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="9"/>
+      <c r="A80" s="10"/>
       <c r="X80" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9"/>
+      <c r="A81" s="10"/>
       <c r="X81" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9"/>
+      <c r="A82" s="10"/>
       <c r="X82" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9"/>
+      <c r="A83" s="10"/>
       <c r="X83" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9"/>
+      <c r="A84" s="10"/>
       <c r="X84" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9"/>
+      <c r="A85" s="10"/>
       <c r="X85" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="9"/>
+      <c r="A86" s="10"/>
       <c r="X86" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9"/>
+      <c r="A87" s="10"/>
       <c r="X87" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9"/>
+      <c r="A88" s="10"/>
       <c r="X88" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9"/>
+      <c r="A89" s="10"/>
       <c r="X89" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9"/>
+      <c r="A90" s="10"/>
       <c r="X90" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="9"/>
+      <c r="A91" s="10"/>
       <c r="X91" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9"/>
+      <c r="A92" s="10"/>
       <c r="X92" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9"/>
+      <c r="A93" s="10"/>
       <c r="X93" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9"/>
+      <c r="A94" s="10"/>
       <c r="X94" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9"/>
+      <c r="A95" s="10"/>
       <c r="X95" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9"/>
+      <c r="A96" s="10"/>
       <c r="X96" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9"/>
+      <c r="A97" s="10"/>
       <c r="X97" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="9"/>
+      <c r="A98" s="10"/>
       <c r="X98" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9"/>
+      <c r="A99" s="10"/>
       <c r="X99" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9"/>
+      <c r="A100" s="10"/>
       <c r="X100" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9"/>
+      <c r="A101" s="10"/>
       <c r="X101" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="9"/>
+      <c r="A102" s="10"/>
       <c r="X102" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9"/>
+      <c r="A103" s="10"/>
       <c r="X103" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9"/>
+      <c r="A104" s="10"/>
       <c r="X104" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9"/>
+      <c r="A105" s="10"/>
       <c r="X105" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9"/>
+      <c r="A106" s="10"/>
       <c r="X106" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9"/>
+      <c r="A107" s="10"/>
       <c r="X107" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -3886,18 +4110,18 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>73</v>
+      <c r="A1" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="str">
+      <c r="A2" s="12" t="str">
         <f t="array" ref="A2:B23">SORT(
 TRANSPOSE({Detail!B2:W2;Detail!B1:W1}),
 2,
@@ -3906,221 +4130,221 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>620.0</v>
+        <v>680.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2">
+        <v>660.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B4" s="2">
+        <v>660.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2">
         <v>600.0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2">
+    <row r="6">
+      <c r="A6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2">
         <v>580.0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2">
+    <row r="7">
+      <c r="A7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2">
+        <v>560.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2">
         <v>540.0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="2">
+    <row r="9">
+      <c r="A9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2">
+        <v>540.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2">
+        <v>540.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2">
+        <v>540.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2">
+        <v>540.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="2">
+        <v>540.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2">
         <v>520.0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2">
-        <v>520.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="2">
-        <v>520.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2">
+    <row r="15">
+      <c r="A15" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2">
         <v>500.0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2">
-        <v>500.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="2">
-        <v>500.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="2">
+    <row r="16">
+      <c r="A16" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2">
         <v>480.0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="2">
+    <row r="17">
+      <c r="A17" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2">
         <v>480.0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2">
+    <row r="18">
+      <c r="A18" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2">
         <v>460.0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="2">
+    <row r="19">
+      <c r="A19" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="2">
         <v>460.0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2">
+    <row r="20">
+      <c r="A20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2">
+        <v>460.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="2">
         <v>440.0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2">
+    <row r="22">
+      <c r="A22" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="2">
         <v>440.0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2">
+    <row r="23">
+      <c r="A23" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="2">
         <v>440.0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="2">
-        <v>420.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" s="2">
-        <v>400.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="2">
-        <v>400.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="2">
-        <v>400.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="2">
-        <v>380.0</v>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="12"/>
+      <c r="A24" s="13"/>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="14">
+      <c r="A25" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>10600</v>
+        <v>11660</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="14">
+      <c r="A26" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>482</v>
+        <v>530</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="15">
+      <c r="A27" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="16">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="14">
+      <c r="A28" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="15">
         <f>(Detail!X1) * 10</f>
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11"/>
+      <c r="A29" s="12"/>
     </row>
     <row r="30">
-      <c r="A30" s="11"/>
+      <c r="A30" s="12"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="84">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -919,14 +919,14 @@
         <b/>
         <color theme="1"/>
       </rPr>
-      <t>Bosnia</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t>-Quatar</t>
+      <t xml:space="preserve">Bosnia </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>- Quatar</t>
     </r>
   </si>
   <si>
@@ -939,14 +939,48 @@
         <b/>
         <color theme="1"/>
       </rPr>
-      <t>Brazil</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t>-Scotland</t>
+      <t xml:space="preserve">Brazil </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>- Scotland</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Hàn Quốc - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Nam Phi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Mexico</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Séc</t>
     </r>
   </si>
   <si>
@@ -1325,31 +1359,31 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
@@ -1357,63 +1391,63 @@
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>640</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>620</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
@@ -3722,17 +3756,102 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10"/>
+      <c r="A55" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V55" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W55" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X55" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10"/>
+      <c r="A56" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G56" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H56" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J56" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P56" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T56" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V56" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X56" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57">
@@ -4111,13 +4230,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2">
@@ -4130,7 +4249,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>680.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="3">
@@ -4138,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>660.0</v>
+        <v>680.0</v>
       </c>
     </row>
     <row r="4">
@@ -4146,7 +4265,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="2">
-        <v>660.0</v>
+        <v>680.0</v>
       </c>
     </row>
     <row r="5">
@@ -4154,7 +4273,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="2">
-        <v>600.0</v>
+        <v>640.0</v>
       </c>
     </row>
     <row r="6">
@@ -4162,47 +4281,47 @@
         <v>20</v>
       </c>
       <c r="B6" s="2">
-        <v>580.0</v>
+        <v>620.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>560.0</v>
+        <v>580.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>540.0</v>
+        <v>580.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2">
-        <v>540.0</v>
+        <v>580.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2">
-        <v>540.0</v>
+        <v>580.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B11" s="2">
-        <v>540.0</v>
+        <v>560.0</v>
       </c>
     </row>
     <row r="12">
@@ -4210,7 +4329,7 @@
         <v>19</v>
       </c>
       <c r="B12" s="2">
-        <v>540.0</v>
+        <v>560.0</v>
       </c>
     </row>
     <row r="13">
@@ -4218,7 +4337,7 @@
         <v>21</v>
       </c>
       <c r="B13" s="2">
-        <v>540.0</v>
+        <v>560.0</v>
       </c>
     </row>
     <row r="14">
@@ -4226,7 +4345,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="2">
-        <v>520.0</v>
+        <v>540.0</v>
       </c>
     </row>
     <row r="15">
@@ -4234,7 +4353,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>500.0</v>
+        <v>520.0</v>
       </c>
     </row>
     <row r="16">
@@ -4242,7 +4361,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="2">
-        <v>480.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="17">
@@ -4250,7 +4369,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="2">
-        <v>480.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="18">
@@ -4258,44 +4377,44 @@
         <v>3</v>
       </c>
       <c r="B18" s="2">
-        <v>460.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B19" s="2">
-        <v>460.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2">
-        <v>460.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>440.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2">
-        <v>440.0</v>
+        <v>460.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2">
         <v>440.0</v>
@@ -4306,38 +4425,38 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>11660</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>530</v>
+        <v>555</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B27" s="16">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B28" s="15">
         <f>(Detail!X1) * 10</f>
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="29">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="90">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -984,6 +984,80 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Bờ Biển Ngà - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Curacao</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Đức - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Ecuador</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Hà Lan - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Tuynidi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Nhật Bản - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Thuỵ Điển</t>
+    </r>
+  </si>
+  <si>
+    <t>Mỹ - Thổ Nhĩ Kì</t>
+  </si>
+  <si>
+    <t>Paraguay - Úc</t>
+  </si>
+  <si>
     <t>Vua đóng góp</t>
   </si>
   <si>
@@ -1002,7 +1076,7 @@
     <t>AVG/trận</t>
   </si>
   <si>
-    <t>XS WIN 50%</t>
+    <t>AVG WIN 50%</t>
   </si>
 </sst>
 </file>
@@ -1363,91 +1437,91 @@
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>640</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>740</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>640</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>640</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>560</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>740</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>620</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>640</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>540</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>640</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>700</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>620</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>700</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>620</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
@@ -3855,42 +3929,264 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10"/>
+      <c r="A57" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C57" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D57" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E57" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F57" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G57" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M57" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N57" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O57" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q57" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V57" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X57" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10"/>
+      <c r="A58" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V58" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W58" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X58" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10"/>
+      <c r="A59" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V59" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W59" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X59" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10"/>
+      <c r="A60" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V60" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W60" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X60" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10"/>
+      <c r="A61" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="X61" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10"/>
+      <c r="A62" s="6" t="s">
+        <v>82</v>
+      </c>
       <c r="X62" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4230,13 +4526,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2">
@@ -4249,103 +4545,103 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>700.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>680.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2">
-        <v>680.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2">
-        <v>640.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B6" s="2">
-        <v>620.0</v>
+        <v>680.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2">
-        <v>580.0</v>
+        <v>640.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2">
-        <v>580.0</v>
+        <v>640.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2">
-        <v>580.0</v>
+        <v>640.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2">
-        <v>580.0</v>
+        <v>640.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2">
-        <v>560.0</v>
+        <v>640.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>560.0</v>
+        <v>620.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2">
-        <v>560.0</v>
+        <v>620.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2">
-        <v>540.0</v>
+        <v>620.0</v>
       </c>
     </row>
     <row r="15">
@@ -4353,63 +4649,63 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>520.0</v>
+        <v>600.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2">
-        <v>500.0</v>
+        <v>580.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2">
-        <v>500.0</v>
+        <v>560.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2">
-        <v>480.0</v>
+        <v>560.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2">
-        <v>480.0</v>
+        <v>560.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2">
-        <v>480.0</v>
+        <v>540.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B21" s="2">
-        <v>480.0</v>
+        <v>540.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
-        <v>460.0</v>
+        <v>540.0</v>
       </c>
     </row>
     <row r="23">
@@ -4417,7 +4713,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>440.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="24">
@@ -4425,38 +4721,38 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>12200</v>
+        <v>13600</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>555</v>
+        <v>618</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B27" s="16">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B28" s="15">
         <f>(Detail!X1) * 10</f>
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="29">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -1052,10 +1052,38 @@
     </r>
   </si>
   <si>
-    <t>Mỹ - Thổ Nhĩ Kì</t>
-  </si>
-  <si>
-    <t>Paraguay - Úc</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Mỹ - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Thổ Nhĩ Kì</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Paraguay - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Úc</t>
+    </r>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1437,91 +1465,91 @@
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>680</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>680</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>660</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>620</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
@@ -4178,18 +4206,99 @@
       <c r="A61" s="6" t="s">
         <v>81</v>
       </c>
+      <c r="C61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V61" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W61" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X61" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
         <v>82</v>
       </c>
+      <c r="D62" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F62" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G62" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K62" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M62" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N62" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O62" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X62" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63">
@@ -4545,7 +4654,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>740.0</v>
+        <v>760.0</v>
       </c>
     </row>
     <row r="3">
@@ -4553,7 +4662,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>740.0</v>
+        <v>760.0</v>
       </c>
     </row>
     <row r="4">
@@ -4561,7 +4670,7 @@
         <v>18</v>
       </c>
       <c r="B4" s="2">
-        <v>700.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="5">
@@ -4569,7 +4678,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="2">
-        <v>700.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="6">
@@ -4585,7 +4694,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="2">
-        <v>640.0</v>
+        <v>680.0</v>
       </c>
     </row>
     <row r="8">
@@ -4593,7 +4702,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="2">
-        <v>640.0</v>
+        <v>680.0</v>
       </c>
     </row>
     <row r="9">
@@ -4601,31 +4710,31 @@
         <v>6</v>
       </c>
       <c r="B9" s="2">
-        <v>640.0</v>
+        <v>660.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>640.0</v>
+        <v>660.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2">
-        <v>640.0</v>
+        <v>660.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2">
-        <v>620.0</v>
+        <v>660.0</v>
       </c>
     </row>
     <row r="13">
@@ -4633,7 +4742,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="2">
-        <v>620.0</v>
+        <v>640.0</v>
       </c>
     </row>
     <row r="14">
@@ -4641,7 +4750,7 @@
         <v>21</v>
       </c>
       <c r="B14" s="2">
-        <v>620.0</v>
+        <v>640.0</v>
       </c>
     </row>
     <row r="15">
@@ -4649,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>600.0</v>
+        <v>620.0</v>
       </c>
     </row>
     <row r="16">
@@ -4657,31 +4766,31 @@
         <v>12</v>
       </c>
       <c r="B16" s="2">
-        <v>580.0</v>
+        <v>620.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2">
-        <v>560.0</v>
+        <v>600.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
-        <v>560.0</v>
+        <v>600.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B19" s="2">
-        <v>560.0</v>
+        <v>580.0</v>
       </c>
     </row>
     <row r="20">
@@ -4689,7 +4798,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="2">
-        <v>540.0</v>
+        <v>560.0</v>
       </c>
     </row>
     <row r="21">
@@ -4697,7 +4806,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="2">
-        <v>540.0</v>
+        <v>560.0</v>
       </c>
     </row>
     <row r="22">
@@ -4705,7 +4814,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="2">
-        <v>540.0</v>
+        <v>560.0</v>
       </c>
     </row>
     <row r="23">
@@ -4713,7 +4822,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>500.0</v>
+        <v>520.0</v>
       </c>
     </row>
     <row r="24">
@@ -4725,7 +4834,7 @@
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>13600</v>
+        <v>14140</v>
       </c>
     </row>
     <row r="26">
@@ -4734,7 +4843,7 @@
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>618</v>
+        <v>643</v>
       </c>
     </row>
     <row r="27">
@@ -4743,7 +4852,7 @@
       </c>
       <c r="B27" s="16">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28">
@@ -4752,7 +4861,7 @@
       </c>
       <c r="B28" s="15">
         <f>(Detail!X1) * 10</f>
-        <v>580</v>
+        <v>600</v>
       </c>
     </row>
     <row r="29">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="96">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1083,6 +1083,80 @@
         <color theme="1"/>
       </rPr>
       <t>Úc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Senegal</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Iraq</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Pháp</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Na Uy</t>
+    </r>
+  </si>
+  <si>
+    <t>Cape Verde - Ả Rập Xê Út</t>
+  </si>
+  <si>
+    <t>Tây Ban Nha - Uruguay</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Bỉ</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - New Zealand</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Ai Cập - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Iran</t>
     </r>
   </si>
   <si>
@@ -1461,95 +1535,95 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>680</v>
+        <v>780</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>680</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>780</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>680</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>820</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>760</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>740</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>580</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>620</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>860</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>740</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>700</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>740</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>620</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>740</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>640</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>800</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>740</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>800</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>720</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2">
@@ -4302,45 +4376,324 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10"/>
+      <c r="A63" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E63" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K63" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L63" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N63" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O63" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T63" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X63" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10"/>
+      <c r="A64" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D64" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E64" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G64" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H64" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R64" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U64" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V64" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X64" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10"/>
+      <c r="A65" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V65" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W65" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X65" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10"/>
+      <c r="A66" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V66" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W66" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X66" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10"/>
+      <c r="A67" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="C67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="H67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V67" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W67" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X67" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10"/>
+      <c r="A68" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U68" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W68" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X68" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>260</v>
       </c>
     </row>
     <row r="69">
@@ -4635,13 +4988,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2">
@@ -4651,18 +5004,18 @@
 2,
 FALSE
 )</f>
-        <v>Tiến Tùng</v>
+        <v>Trung Ngôn</v>
       </c>
       <c r="B2" s="2">
-        <v>760.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>760.0</v>
+        <v>820.0</v>
       </c>
     </row>
     <row r="4">
@@ -4670,7 +5023,7 @@
         <v>18</v>
       </c>
       <c r="B4" s="2">
-        <v>720.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="5">
@@ -4678,7 +5031,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="2">
-        <v>720.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="6">
@@ -4686,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="B6" s="2">
-        <v>680.0</v>
+        <v>780.0</v>
       </c>
     </row>
     <row r="7">
@@ -4694,7 +5047,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="2">
-        <v>680.0</v>
+        <v>780.0</v>
       </c>
     </row>
     <row r="8">
@@ -4702,7 +5055,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="2">
-        <v>680.0</v>
+        <v>760.0</v>
       </c>
     </row>
     <row r="9">
@@ -4710,7 +5063,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="2">
-        <v>660.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="10">
@@ -4718,7 +5071,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>660.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="11">
@@ -4726,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="2">
-        <v>660.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="12">
@@ -4734,7 +5087,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="2">
-        <v>660.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="13">
@@ -4742,7 +5095,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="2">
-        <v>640.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="14">
@@ -4750,15 +5103,15 @@
         <v>21</v>
       </c>
       <c r="B14" s="2">
-        <v>640.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2">
-        <v>620.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="16">
@@ -4766,55 +5119,55 @@
         <v>12</v>
       </c>
       <c r="B16" s="2">
-        <v>620.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>600.0</v>
+        <v>680.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B18" s="2">
-        <v>600.0</v>
+        <v>680.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2">
-        <v>580.0</v>
+        <v>680.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2">
-        <v>560.0</v>
+        <v>640.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2">
-        <v>560.0</v>
+        <v>620.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2">
-        <v>560.0</v>
+        <v>620.0</v>
       </c>
     </row>
     <row r="23">
@@ -4822,7 +5175,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>520.0</v>
+        <v>580.0</v>
       </c>
     </row>
     <row r="24">
@@ -4830,38 +5183,38 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>14140</v>
+        <v>15920</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>643</v>
+        <v>724</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B27" s="16">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B28" s="15">
         <f>(Detail!X1) * 10</f>
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="29">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="102">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1158,6 +1158,80 @@
       </rPr>
       <t>Iran</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Anh - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Panama</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Croatia</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Ghana</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Bồ Đào Nha - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Colombia</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Congo</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Uzbekistan</t>
+    </r>
+  </si>
+  <si>
+    <t>Áo - Algeria</t>
+  </si>
+  <si>
+    <t>Argentina - Jordan</t>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1535,27 +1609,27 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>780</v>
+        <v>820</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>820</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>820</v>
+        <v>860</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>820</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -1563,67 +1637,67 @@
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>660</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>740</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>720</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>760</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2">
@@ -4697,42 +4771,151 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10"/>
+      <c r="A69" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="D69" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E69" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F69" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G69" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L69" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N69" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O69" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="Q69" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T69" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W69" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X69" s="2">
         <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B70" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F70" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G70" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U70" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W70" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X70" s="2">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="I71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="K71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="R71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="T71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V71" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X71" s="2">
+        <f t="shared" si="2"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B72" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="U72" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="X72" s="2">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="X73" s="2">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="10"/>
-      <c r="X70" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10"/>
-      <c r="X71" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="10"/>
-      <c r="X72" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10"/>
-      <c r="X73" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="74">
-      <c r="A74" s="10"/>
+      <c r="A74" s="6" t="s">
+        <v>94</v>
+      </c>
       <c r="X74" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4988,13 +5171,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
@@ -5007,7 +5190,7 @@
         <v>Trung Ngôn</v>
       </c>
       <c r="B2" s="2">
-        <v>860.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="3">
@@ -5015,7 +5198,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>820.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="4">
@@ -5023,47 +5206,47 @@
         <v>18</v>
       </c>
       <c r="B4" s="2">
-        <v>800.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B5" s="2">
-        <v>800.0</v>
+        <v>820.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>780.0</v>
+        <v>820.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>780.0</v>
+        <v>820.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>760.0</v>
+        <v>820.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2">
-        <v>740.0</v>
+        <v>780.0</v>
       </c>
     </row>
     <row r="10">
@@ -5071,7 +5254,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>740.0</v>
+        <v>760.0</v>
       </c>
     </row>
     <row r="11">
@@ -5079,7 +5262,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="2">
-        <v>740.0</v>
+        <v>760.0</v>
       </c>
     </row>
     <row r="12">
@@ -5087,79 +5270,79 @@
         <v>16</v>
       </c>
       <c r="B12" s="2">
-        <v>740.0</v>
+        <v>760.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2">
-        <v>740.0</v>
+        <v>760.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B14" s="2">
-        <v>720.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2">
-        <v>700.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2">
-        <v>700.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2">
-        <v>680.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>680.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B19" s="2">
-        <v>680.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2">
-        <v>640.0</v>
+        <v>660.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>620.0</v>
+        <v>660.0</v>
       </c>
     </row>
     <row r="22">
@@ -5167,7 +5350,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="2">
-        <v>620.0</v>
+        <v>640.0</v>
       </c>
     </row>
     <row r="23">
@@ -5175,7 +5358,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>580.0</v>
+        <v>600.0</v>
       </c>
     </row>
     <row r="24">
@@ -5183,38 +5366,38 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>15920</v>
+        <v>16560</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>724</v>
+        <v>753</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B27" s="16">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B28" s="15">
         <f>(Detail!X1) * 10</f>
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="29">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -1228,10 +1228,38 @@
     </r>
   </si>
   <si>
-    <t>Áo - Algeria</t>
-  </si>
-  <si>
-    <t>Argentina - Jordan</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Áo - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Algeria</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Argentina - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Jordan</t>
+    </r>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1617,7 +1645,7 @@
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>820</v>
+        <v>860</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
@@ -1625,11 +1653,11 @@
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>820</v>
+        <v>840</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -1641,7 +1669,7 @@
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
@@ -1649,23 +1677,23 @@
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>880</v>
+        <v>920</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>760</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
@@ -1677,7 +1705,7 @@
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>700</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
@@ -1689,15 +1717,15 @@
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>820</v>
+        <v>860</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
@@ -4907,18 +4935,84 @@
       <c r="A73" s="6" t="s">
         <v>93</v>
       </c>
+      <c r="D73" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F73" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="G73" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="J73" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L73" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M73" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N73" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O73" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P73" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S73" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V73" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W73" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X73" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
         <v>94</v>
       </c>
+      <c r="D74" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F74" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="L74" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="M74" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="N74" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="O74" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="P74" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="S74" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="V74" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="W74" s="7">
+        <v>20.0</v>
+      </c>
       <c r="X74" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75">
@@ -5190,7 +5284,7 @@
         <v>Trung Ngôn</v>
       </c>
       <c r="B2" s="2">
-        <v>880.0</v>
+        <v>920.0</v>
       </c>
     </row>
     <row r="3">
@@ -5198,44 +5292,44 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>860.0</v>
+        <v>900.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>840.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2">
-        <v>820.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>820.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2">
-        <v>820.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B8" s="2">
         <v>820.0</v>
@@ -5243,71 +5337,71 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>780.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2">
-        <v>760.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2">
-        <v>760.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>760.0</v>
+        <v>780.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2">
-        <v>760.0</v>
+        <v>780.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>740.0</v>
+        <v>760.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>740.0</v>
+        <v>760.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2">
-        <v>720.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2">
         <v>720.0</v>
@@ -5331,18 +5425,18 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2">
-        <v>660.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2">
-        <v>660.0</v>
+        <v>680.0</v>
       </c>
     </row>
     <row r="22">
@@ -5370,7 +5464,7 @@
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>16560</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="26">
@@ -5379,7 +5473,7 @@
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>753</v>
+        <v>773</v>
       </c>
     </row>
     <row r="27">
@@ -5388,7 +5482,7 @@
       </c>
       <c r="B27" s="16">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28">
@@ -5397,7 +5491,7 @@
       </c>
       <c r="B28" s="15">
         <f>(Detail!X1) * 10</f>
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="29">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -1262,6 +1262,23 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Canada</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Nam Phi</t>
+    </r>
+  </si>
+  <si>
     <t>Vua đóng góp</t>
   </si>
   <si>
@@ -1278,9 +1295,6 @@
   </si>
   <si>
     <t>AVG/trận</t>
-  </si>
-  <si>
-    <t>AVG WIN 50%</t>
   </si>
 </sst>
 </file>
@@ -1637,7 +1651,7 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>820</v>
+        <v>870</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
@@ -1689,11 +1703,11 @@
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>810</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
@@ -1725,7 +1739,7 @@
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
@@ -5016,10 +5030,21 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="10"/>
+      <c r="A75" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B75" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O75" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P75" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X75" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76">
@@ -5265,13 +5290,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
@@ -5297,15 +5322,15 @@
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B4" s="2">
-        <v>860.0</v>
+        <v>870.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2">
         <v>860.0</v>
@@ -5313,47 +5338,47 @@
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2">
-        <v>840.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2">
-        <v>840.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2">
-        <v>820.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2">
-        <v>800.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2">
-        <v>800.0</v>
+        <v>810.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2">
         <v>800.0</v>
@@ -5361,15 +5386,15 @@
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2">
-        <v>780.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2">
         <v>780.0</v>
@@ -5377,10 +5402,10 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>760.0</v>
+        <v>780.0</v>
       </c>
     </row>
     <row r="15">
@@ -5460,39 +5485,34 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>17000</v>
+        <v>17150</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>773</v>
+        <v>780</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="16">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" s="15">
-        <f>(Detail!X1) * 10</f>
-        <v>720</v>
-      </c>
+      <c r="A28" s="14"/>
+      <c r="B28" s="15"/>
     </row>
     <row r="29">
       <c r="A29" s="12"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="105">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1277,6 +1277,43 @@
       </rPr>
       <t xml:space="preserve"> - Nam Phi</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Brazil</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Nhật Bản</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Đức - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Paraguay</t>
+    </r>
+  </si>
+  <si>
+    <t>Hà Lan - Ma Rốc</t>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1651,7 +1688,7 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>870</v>
+        <v>920</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
@@ -1663,15 +1700,15 @@
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>940</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -1683,7 +1720,7 @@
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>730</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
@@ -1699,11 +1736,11 @@
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>830</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>860</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
@@ -1723,11 +1760,11 @@
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>890</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>830</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
@@ -1735,11 +1772,11 @@
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2">
@@ -5048,21 +5085,63 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="10"/>
+      <c r="A76" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B76" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E76" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F76" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G76" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="U76" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X76" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10"/>
+      <c r="A77" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F77" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G77" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J77" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N77" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O77" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T77" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W77" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X77" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="10"/>
+      <c r="A78" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="X78" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5290,13 +5369,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2">
@@ -5306,18 +5385,18 @@
 2,
 FALSE
 )</f>
-        <v>Trung Ngôn</v>
+        <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>920.0</v>
+        <v>1000.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>900.0</v>
+        <v>940.0</v>
       </c>
     </row>
     <row r="4">
@@ -5325,87 +5404,87 @@
         <v>0</v>
       </c>
       <c r="B4" s="2">
-        <v>870.0</v>
+        <v>920.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>860.0</v>
+        <v>920.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2">
-        <v>860.0</v>
+        <v>890.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2">
-        <v>850.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2">
-        <v>840.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2">
-        <v>840.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2">
-        <v>810.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2">
-        <v>800.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>800.0</v>
+        <v>830.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2">
-        <v>780.0</v>
+        <v>830.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2">
-        <v>780.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="15">
@@ -5418,39 +5497,39 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B16" s="2">
-        <v>740.0</v>
+        <v>750.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B17" s="2">
-        <v>720.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2">
-        <v>700.0</v>
+        <v>730.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2">
-        <v>700.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B20" s="2">
         <v>700.0</v>
@@ -5458,10 +5537,10 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>680.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="22">
@@ -5485,29 +5564,29 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>17150</v>
+        <v>17750</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>780</v>
+        <v>807</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B27" s="16">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -1313,7 +1313,21 @@
     </r>
   </si>
   <si>
-    <t>Hà Lan - Ma Rốc</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Hà Lan - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Ma Rốc</t>
+    </r>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1688,7 +1702,7 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>920</v>
+        <v>970</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
@@ -1696,7 +1710,7 @@
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>860</v>
+        <v>910</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
@@ -1704,7 +1718,7 @@
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
@@ -1716,7 +1730,7 @@
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
@@ -1724,7 +1738,7 @@
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>770</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
@@ -1732,19 +1746,19 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>830</v>
+        <v>880</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>860</v>
+        <v>910</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
@@ -1752,11 +1766,11 @@
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>810</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
@@ -1776,7 +1790,7 @@
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
@@ -5142,9 +5156,42 @@
       <c r="A78" s="6" t="s">
         <v>98</v>
       </c>
+      <c r="B78" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="D78" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F78" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="I78" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K78" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M78" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N78" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O78" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P78" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R78" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S78" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X78" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>550</v>
       </c>
     </row>
     <row r="79">
@@ -5388,23 +5435,23 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>1000.0</v>
+        <v>1050.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>940.0</v>
+        <v>970.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>920.0</v>
+        <v>940.0</v>
       </c>
     </row>
     <row r="5">
@@ -5417,74 +5464,74 @@
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>890.0</v>
+        <v>910.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2">
-        <v>860.0</v>
+        <v>910.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2">
-        <v>860.0</v>
+        <v>900.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2">
-        <v>860.0</v>
+        <v>890.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>850.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2">
-        <v>850.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>830.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2">
-        <v>830.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>800.0</v>
+        <v>830.0</v>
       </c>
     </row>
     <row r="15">
@@ -5492,52 +5539,52 @@
         <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>760.0</v>
+        <v>810.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2">
-        <v>750.0</v>
+        <v>770.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2">
-        <v>740.0</v>
+        <v>750.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>730.0</v>
+        <v>750.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B19" s="2">
-        <v>720.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2">
-        <v>700.0</v>
+        <v>730.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B21" s="2">
         <v>700.0</v>
@@ -5545,18 +5592,18 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B22" s="2">
-        <v>640.0</v>
+        <v>650.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B23" s="2">
-        <v>600.0</v>
+        <v>640.0</v>
       </c>
     </row>
     <row r="24">
@@ -5568,7 +5615,7 @@
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>17750</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="26">
@@ -5577,7 +5624,7 @@
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>807</v>
+        <v>832</v>
       </c>
     </row>
     <row r="27">
@@ -5586,7 +5633,7 @@
       </c>
       <c r="B27" s="16">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="109">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1328,6 +1328,46 @@
       </rPr>
       <t>Ma Rốc</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Na Uy</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Bờ Biển Ngà</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Pháp </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>- Thuỵ Điển</t>
+    </r>
+  </si>
+  <si>
+    <t>Mexico - Ecuador</t>
+  </si>
+  <si>
+    <t>Anh - Congo</t>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1702,7 +1742,7 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>970</v>
+        <v>1070</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
@@ -1718,11 +1758,11 @@
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>940</v>
+        <v>990</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -1738,15 +1778,15 @@
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>770</v>
+        <v>820</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>920</v>
+        <v>970</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
@@ -1766,11 +1806,11 @@
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>860</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
@@ -1790,7 +1830,7 @@
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2">
@@ -5195,28 +5235,63 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10"/>
+      <c r="A79" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B79" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F79" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L79" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M79" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R79" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X79" s="2">
         <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G80" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K80" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S80" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="X80" s="2">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="X81" s="2">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="10"/>
-      <c r="X80" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10"/>
-      <c r="X81" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="10"/>
+      <c r="A82" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="X82" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5416,13 +5491,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2">
@@ -5435,7 +5510,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>1050.0</v>
+        <v>1100.0</v>
       </c>
     </row>
     <row r="3">
@@ -5443,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>970.0</v>
+        <v>1070.0</v>
       </c>
     </row>
     <row r="4">
@@ -5451,7 +5526,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>940.0</v>
+        <v>990.0</v>
       </c>
     </row>
     <row r="5">
@@ -5459,7 +5534,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>920.0</v>
+        <v>970.0</v>
       </c>
     </row>
     <row r="6">
@@ -5480,7 +5555,7 @@
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2">
         <v>900.0</v>
@@ -5488,58 +5563,58 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2">
-        <v>890.0</v>
+        <v>900.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2">
-        <v>880.0</v>
+        <v>890.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2">
-        <v>860.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2">
-        <v>850.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2">
-        <v>850.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2">
-        <v>830.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2">
-        <v>810.0</v>
+        <v>830.0</v>
       </c>
     </row>
     <row r="16">
@@ -5547,20 +5622,20 @@
         <v>9</v>
       </c>
       <c r="B16" s="2">
-        <v>770.0</v>
+        <v>820.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>750.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B18" s="2">
         <v>750.0</v>
@@ -5611,29 +5686,29 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>18300</v>
+        <v>18750</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>832</v>
+        <v>852</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B27" s="16">
         <f>Round(B25/(Detail!X1),0)</f>
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="110">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1364,12 +1364,32 @@
     </r>
   </si>
   <si>
-    <t>Mexico - Ecuador</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Mexico</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Ecuador</t>
+    </r>
   </si>
   <si>
     <t>Anh - Congo</t>
   </si>
   <si>
+    <t>Bỉ  - Senegal</t>
+  </si>
+  <si>
+    <t>Mỹ - Bosnia</t>
+  </si>
+  <si>
     <t>Vua đóng góp</t>
   </si>
   <si>
@@ -1383,9 +1403,6 @@
   </si>
   <si>
     <t>AVG/người</t>
-  </si>
-  <si>
-    <t>AVG/trận</t>
   </si>
 </sst>
 </file>
@@ -1742,23 +1759,23 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>1070</v>
+        <v>1120</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>910</v>
+        <v>960</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
@@ -1766,11 +1783,11 @@
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>740</v>
+        <v>790</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
@@ -1782,7 +1799,7 @@
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>970</v>
+        <v>1020</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
@@ -1794,7 +1811,7 @@
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>910</v>
+        <v>960</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
@@ -1802,7 +1819,7 @@
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>690</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
@@ -1822,15 +1839,15 @@
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>860</v>
+        <v>910</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2">
@@ -5283,9 +5300,45 @@
       <c r="A81" s="6" t="s">
         <v>101</v>
       </c>
+      <c r="B81" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="C81" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="D81" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E81" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F81" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="H81" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="I81" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L81" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O81" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q81" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V81" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W81" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X81" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="82">
@@ -5298,14 +5351,18 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10"/>
+      <c r="A83" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="X83" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="10"/>
+      <c r="A84" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="X84" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5491,13 +5548,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2">
@@ -5510,7 +5567,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>1100.0</v>
+        <v>1150.0</v>
       </c>
     </row>
     <row r="3">
@@ -5518,23 +5575,23 @@
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>1070.0</v>
+        <v>1120.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
-        <v>990.0</v>
+        <v>1020.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>970.0</v>
+        <v>990.0</v>
       </c>
     </row>
     <row r="6">
@@ -5542,7 +5599,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>910.0</v>
+        <v>960.0</v>
       </c>
     </row>
     <row r="7">
@@ -5550,20 +5607,20 @@
         <v>13</v>
       </c>
       <c r="B7" s="2">
-        <v>910.0</v>
+        <v>960.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>900.0</v>
+        <v>910.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2">
         <v>900.0</v>
@@ -5571,42 +5628,42 @@
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2">
-        <v>890.0</v>
+        <v>900.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2">
-        <v>880.0</v>
+        <v>900.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2">
-        <v>860.0</v>
+        <v>890.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>860.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
-        <v>850.0</v>
+        <v>860.0</v>
       </c>
     </row>
     <row r="15">
@@ -5627,7 +5684,7 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2">
         <v>800.0</v>
@@ -5635,10 +5692,10 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>750.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="19">
@@ -5646,23 +5703,23 @@
         <v>6</v>
       </c>
       <c r="B19" s="2">
-        <v>740.0</v>
+        <v>790.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>730.0</v>
+        <v>750.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2">
-        <v>700.0</v>
+        <v>730.0</v>
       </c>
     </row>
     <row r="22">
@@ -5670,7 +5727,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="2">
-        <v>650.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="23">
@@ -5678,7 +5735,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="2">
-        <v>640.0</v>
+        <v>690.0</v>
       </c>
     </row>
     <row r="24">
@@ -5686,30 +5743,25 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>18750</v>
+        <v>19350</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>852</v>
+        <v>880</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B27" s="16">
-        <f>Round(B25/(Detail!X1),0)</f>
-        <v>240</v>
-      </c>
+      <c r="A27" s="14"/>
+      <c r="B27" s="16"/>
     </row>
     <row r="28">
       <c r="A28" s="14"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -1381,7 +1381,21 @@
     </r>
   </si>
   <si>
-    <t>Anh - Congo</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Anh - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Congo</t>
+    </r>
   </si>
   <si>
     <t>Bỉ  - Senegal</t>
@@ -1763,7 +1777,7 @@
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
@@ -1771,19 +1785,19 @@
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>990</v>
+        <v>1040</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>790</v>
+        <v>840</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
@@ -1791,7 +1805,7 @@
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>730</v>
+        <v>780</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
@@ -1807,23 +1821,23 @@
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>880</v>
+        <v>930</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>960</v>
+        <v>1010</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>690</v>
+        <v>740</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>860</v>
+        <v>910</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
@@ -1831,7 +1845,7 @@
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>890</v>
+        <v>940</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
@@ -1839,15 +1853,15 @@
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>910</v>
+        <v>960</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2">
@@ -5345,9 +5359,51 @@
       <c r="A82" s="6" t="s">
         <v>102</v>
       </c>
+      <c r="C82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="H82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V82" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W82" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X82" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="83">
@@ -5567,7 +5623,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>1150.0</v>
+        <v>1200.0</v>
       </c>
     </row>
     <row r="3">
@@ -5580,31 +5636,31 @@
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>1020.0</v>
+        <v>1040.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>990.0</v>
+        <v>1020.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
-        <v>960.0</v>
+        <v>1010.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2">
         <v>960.0</v>
@@ -5615,103 +5671,103 @@
         <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>910.0</v>
+        <v>960.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2">
-        <v>900.0</v>
+        <v>950.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>900.0</v>
+        <v>950.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2">
-        <v>900.0</v>
+        <v>940.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>890.0</v>
+        <v>930.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
-        <v>880.0</v>
+        <v>910.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2">
-        <v>860.0</v>
+        <v>900.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B15" s="2">
-        <v>830.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2">
-        <v>820.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2">
-        <v>800.0</v>
+        <v>830.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2">
-        <v>800.0</v>
+        <v>820.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>790.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2">
-        <v>750.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="21">
@@ -5719,23 +5775,23 @@
         <v>8</v>
       </c>
       <c r="B21" s="2">
-        <v>730.0</v>
+        <v>780.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2">
-        <v>700.0</v>
+        <v>740.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>690.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="24">
@@ -5747,7 +5803,7 @@
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>19350</v>
+        <v>20050</v>
       </c>
     </row>
     <row r="26">
@@ -5756,7 +5812,7 @@
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>880</v>
+        <v>911</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -1398,7 +1398,21 @@
     </r>
   </si>
   <si>
-    <t>Bỉ  - Senegal</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Bỉ  - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Senegal</t>
+    </r>
   </si>
   <si>
     <t>Mỹ - Bosnia</t>
@@ -1777,15 +1791,15 @@
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>960</v>
+        <v>1010</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
@@ -1797,31 +1811,31 @@
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>890</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>830</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>820</v>
+        <v>870</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>1020</v>
+        <v>1070</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>930</v>
+        <v>980</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
@@ -1829,23 +1843,23 @@
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>740</v>
+        <v>790</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>910</v>
+        <v>960</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>940</v>
+        <v>990</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
@@ -1853,15 +1867,15 @@
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>960</v>
+        <v>1010</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2">
@@ -5410,9 +5424,60 @@
       <c r="A83" s="6" t="s">
         <v>103</v>
       </c>
+      <c r="C83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="D83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="H83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="I83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V83" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W83" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X83" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>850</v>
       </c>
     </row>
     <row r="84">
@@ -5636,23 +5701,23 @@
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
-        <v>1040.0</v>
+        <v>1070.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>1020.0</v>
+        <v>1040.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2">
         <v>1010.0</v>
@@ -5660,10 +5725,10 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2">
-        <v>960.0</v>
+        <v>1010.0</v>
       </c>
     </row>
     <row r="8">
@@ -5671,7 +5736,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>960.0</v>
+        <v>1010.0</v>
       </c>
     </row>
     <row r="9">
@@ -5679,7 +5744,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="2">
-        <v>950.0</v>
+        <v>1000.0</v>
       </c>
     </row>
     <row r="10">
@@ -5687,7 +5752,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>950.0</v>
+        <v>1000.0</v>
       </c>
     </row>
     <row r="11">
@@ -5695,7 +5760,7 @@
         <v>18</v>
       </c>
       <c r="B11" s="2">
-        <v>940.0</v>
+        <v>990.0</v>
       </c>
     </row>
     <row r="12">
@@ -5703,7 +5768,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>930.0</v>
+        <v>980.0</v>
       </c>
     </row>
     <row r="13">
@@ -5711,7 +5776,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="2">
-        <v>910.0</v>
+        <v>960.0</v>
       </c>
     </row>
     <row r="14">
@@ -5719,7 +5784,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="2">
-        <v>900.0</v>
+        <v>950.0</v>
       </c>
     </row>
     <row r="15">
@@ -5727,7 +5792,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="2">
-        <v>850.0</v>
+        <v>900.0</v>
       </c>
     </row>
     <row r="16">
@@ -5735,47 +5800,47 @@
         <v>6</v>
       </c>
       <c r="B16" s="2">
-        <v>840.0</v>
+        <v>890.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2">
-        <v>830.0</v>
+        <v>870.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>820.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>800.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2">
-        <v>800.0</v>
+        <v>830.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>780.0</v>
+        <v>830.0</v>
       </c>
     </row>
     <row r="22">
@@ -5783,7 +5848,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="2">
-        <v>740.0</v>
+        <v>790.0</v>
       </c>
     </row>
     <row r="23">
@@ -5791,7 +5856,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>700.0</v>
+        <v>750.0</v>
       </c>
     </row>
     <row r="24">
@@ -5803,7 +5868,7 @@
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>20050</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="26">
@@ -5812,7 +5877,7 @@
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>911</v>
+        <v>950</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -1415,7 +1415,21 @@
     </r>
   </si>
   <si>
-    <t>Mỹ - Bosnia</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Mỹ</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Bosnia</t>
+    </r>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1787,7 +1801,7 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>1120</v>
+        <v>1170</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
@@ -1799,11 +1813,11 @@
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
@@ -1811,7 +1825,7 @@
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>890</v>
+        <v>940</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
@@ -1847,7 +1861,7 @@
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>790</v>
+        <v>840</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
@@ -1863,7 +1877,7 @@
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>830</v>
+        <v>880</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
@@ -1875,7 +1889,7 @@
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2">
@@ -5484,9 +5498,27 @@
       <c r="A84" s="6" t="s">
         <v>104</v>
       </c>
+      <c r="B84" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E84" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F84" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="H84" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q84" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="U84" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X84" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85">
@@ -5688,7 +5720,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>1200.0</v>
+        <v>1250.0</v>
       </c>
     </row>
     <row r="3">
@@ -5696,7 +5728,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>1120.0</v>
+        <v>1170.0</v>
       </c>
     </row>
     <row r="4">
@@ -5781,7 +5813,7 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2">
         <v>950.0</v>
@@ -5789,10 +5821,10 @@
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>900.0</v>
+        <v>950.0</v>
       </c>
     </row>
     <row r="16">
@@ -5800,28 +5832,28 @@
         <v>6</v>
       </c>
       <c r="B16" s="2">
-        <v>890.0</v>
+        <v>940.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2">
-        <v>870.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2">
-        <v>850.0</v>
+        <v>870.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B19" s="2">
         <v>850.0</v>
@@ -5829,26 +5861,26 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2">
-        <v>830.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B21" s="2">
-        <v>830.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B22" s="2">
-        <v>790.0</v>
+        <v>830.0</v>
       </c>
     </row>
     <row r="23">
@@ -5868,7 +5900,7 @@
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>20900</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="26">
@@ -5877,7 +5909,7 @@
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>950</v>
+        <v>964</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="113">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1430,6 +1430,43 @@
       </rPr>
       <t xml:space="preserve"> - Bosnia</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Tây Ban Nha</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Áo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Bồ Đào Nha </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>- Croatia</t>
+    </r>
+  </si>
+  <si>
+    <t>Thuỵ Sĩ - Algeria</t>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1801,7 +1838,7 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>1170</v>
+        <v>1270</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
@@ -1817,15 +1854,15 @@
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>1040</v>
+        <v>1090</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>940</v>
+        <v>990</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
@@ -1833,11 +1870,11 @@
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>830</v>
+        <v>930</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>870</v>
+        <v>920</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
@@ -1845,7 +1882,7 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
@@ -1865,15 +1902,15 @@
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>960</v>
+        <v>1010</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>990</v>
+        <v>1040</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
@@ -1885,11 +1922,11 @@
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2">
@@ -5522,21 +5559,69 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10"/>
+      <c r="A85" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G85" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="H85" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J85" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K85" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R85" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T85" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W85" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X85" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="10"/>
+      <c r="A86" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F86" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J86" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M86" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S86" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W86" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X86" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="10"/>
+      <c r="A87" s="6" t="s">
+        <v>107</v>
+      </c>
       <c r="X87" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5701,13 +5786,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2">
@@ -5720,7 +5805,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>1250.0</v>
+        <v>1300.0</v>
       </c>
     </row>
     <row r="3">
@@ -5728,15 +5813,15 @@
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>1170.0</v>
+        <v>1270.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
-        <v>1070.0</v>
+        <v>1100.0</v>
       </c>
     </row>
     <row r="5">
@@ -5744,28 +5829,28 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>1040.0</v>
+        <v>1090.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>1010.0</v>
+        <v>1070.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2">
-        <v>1010.0</v>
+        <v>1040.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2">
         <v>1010.0</v>
@@ -5773,74 +5858,74 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2">
-        <v>1000.0</v>
+        <v>1010.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2">
-        <v>1000.0</v>
+        <v>1010.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2">
-        <v>990.0</v>
+        <v>1010.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>980.0</v>
+        <v>1000.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>960.0</v>
+        <v>1000.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B14" s="2">
-        <v>950.0</v>
+        <v>990.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2">
-        <v>950.0</v>
+        <v>980.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B16" s="2">
-        <v>940.0</v>
+        <v>950.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B17" s="2">
-        <v>880.0</v>
+        <v>930.0</v>
       </c>
     </row>
     <row r="18">
@@ -5848,39 +5933,39 @@
         <v>9</v>
       </c>
       <c r="B18" s="2">
-        <v>870.0</v>
+        <v>920.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>850.0</v>
+        <v>900.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>850.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>840.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2">
-        <v>830.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="23">
@@ -5896,20 +5981,20 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>21200</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>964</v>
+        <v>995</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="116">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1466,7 +1466,30 @@
     </r>
   </si>
   <si>
-    <t>Thuỵ Sĩ - Algeria</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Thuỵ Sĩ </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>- Algeria</t>
+    </r>
+  </si>
+  <si>
+    <t>Ai Cập - Úc</t>
+  </si>
+  <si>
+    <t>Argentina - Cape Verde</t>
+  </si>
+  <si>
+    <t>Colombia - Ghana</t>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1838,15 +1861,15 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>1270</v>
+        <v>1320</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>1010</v>
+        <v>1060</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
@@ -1858,15 +1881,15 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>1090</v>
+        <v>1140</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>990</v>
+        <v>1040</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
@@ -1890,7 +1913,7 @@
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>1010</v>
+        <v>1060</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
@@ -1922,11 +1945,11 @@
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2">
@@ -5622,27 +5645,57 @@
       <c r="A87" s="6" t="s">
         <v>107</v>
       </c>
+      <c r="B87" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="C87" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="D87" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G87" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="H87" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="I87" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O87" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W87" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X87" s="2">
         <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="X88" s="2">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="10"/>
-      <c r="X88" s="2">
+    <row r="89">
+      <c r="A89" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="X89" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="10"/>
-      <c r="X89" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="90">
-      <c r="A90" s="10"/>
+      <c r="A90" s="6" t="s">
+        <v>110</v>
+      </c>
       <c r="X90" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5786,13 +5839,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2">
@@ -5802,18 +5855,18 @@
 2,
 FALSE
 )</f>
-        <v>Tiến Tùng</v>
+        <v>Thái Bình</v>
       </c>
       <c r="B2" s="2">
-        <v>1300.0</v>
+        <v>1320.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>1270.0</v>
+        <v>1300.0</v>
       </c>
     </row>
     <row r="4">
@@ -5821,7 +5874,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="2">
-        <v>1100.0</v>
+        <v>1150.0</v>
       </c>
     </row>
     <row r="5">
@@ -5829,7 +5882,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>1090.0</v>
+        <v>1140.0</v>
       </c>
     </row>
     <row r="6">
@@ -5842,39 +5895,39 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2">
-        <v>1040.0</v>
+        <v>1060.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2">
-        <v>1010.0</v>
+        <v>1060.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2">
-        <v>1010.0</v>
+        <v>1040.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2">
-        <v>1010.0</v>
+        <v>1040.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2">
         <v>1010.0</v>
@@ -5882,15 +5935,15 @@
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2">
-        <v>1000.0</v>
+        <v>1010.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
         <v>1000.0</v>
@@ -5898,10 +5951,10 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>990.0</v>
+        <v>1000.0</v>
       </c>
     </row>
     <row r="15">
@@ -5938,7 +5991,7 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B19" s="2">
         <v>900.0</v>
@@ -5946,18 +5999,18 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2">
-        <v>880.0</v>
+        <v>900.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>850.0</v>
+        <v>880.0</v>
       </c>
     </row>
     <row r="22">
@@ -5973,7 +6026,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>750.0</v>
+        <v>800.0</v>
       </c>
     </row>
     <row r="24">
@@ -5981,20 +6034,20 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>21900</v>
+        <v>22300</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>995</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -1483,13 +1483,43 @@
     </r>
   </si>
   <si>
-    <t>Ai Cập - Úc</t>
-  </si>
-  <si>
-    <t>Argentina - Cape Verde</t>
-  </si>
-  <si>
-    <t>Colombia - Ghana</t>
+    <r>
+      <t xml:space="preserve">Ai Cập - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Úc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Argentina - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Cape Verde</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Colombia - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Ghana</t>
+    </r>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1865,55 +1895,55 @@
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>950</v>
+        <v>1050</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1450</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>1140</v>
+        <v>1190</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>1040</v>
+        <v>1090</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>930</v>
+        <v>980</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>920</v>
+        <v>970</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>1070</v>
+        <v>1120</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>980</v>
+        <v>1080</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>1060</v>
+        <v>1210</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
@@ -1921,7 +1951,7 @@
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>940</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
@@ -1929,27 +1959,27 @@
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>1040</v>
+        <v>1090</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>880</v>
+        <v>930</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>1010</v>
+        <v>1060</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>1150</v>
+        <v>1250</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2">
@@ -5678,27 +5708,114 @@
       <c r="A88" s="6" t="s">
         <v>108</v>
       </c>
+      <c r="D88" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F88" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G88" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="I88" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K88" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M88" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N88" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O88" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="U88" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X88" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>450</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
         <v>109</v>
       </c>
+      <c r="C89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="H89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V89" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W89" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X89" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>650</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
         <v>110</v>
       </c>
+      <c r="C90" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E90" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F90" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N90" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O90" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q90" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W90" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X90" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="91">
@@ -5855,18 +5972,18 @@
 2,
 FALSE
 )</f>
-        <v>Thái Bình</v>
+        <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>1320.0</v>
+        <v>1450.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>1300.0</v>
+        <v>1320.0</v>
       </c>
     </row>
     <row r="4">
@@ -5874,127 +5991,127 @@
         <v>21</v>
       </c>
       <c r="B4" s="2">
-        <v>1150.0</v>
+        <v>1250.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2">
-        <v>1140.0</v>
+        <v>1210.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>1070.0</v>
+        <v>1190.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2">
-        <v>1060.0</v>
+        <v>1120.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2">
-        <v>1060.0</v>
+        <v>1110.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>1040.0</v>
+        <v>1100.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>1040.0</v>
+        <v>1090.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2">
-        <v>1010.0</v>
+        <v>1090.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>1010.0</v>
+        <v>1080.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2">
-        <v>1000.0</v>
+        <v>1060.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2">
-        <v>1000.0</v>
+        <v>1050.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>980.0</v>
+        <v>1010.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>950.0</v>
+        <v>1000.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B17" s="2">
-        <v>930.0</v>
+        <v>1000.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2">
-        <v>920.0</v>
+        <v>980.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2">
-        <v>900.0</v>
+        <v>970.0</v>
       </c>
     </row>
     <row r="20">
@@ -6002,23 +6119,23 @@
         <v>17</v>
       </c>
       <c r="B20" s="2">
-        <v>900.0</v>
+        <v>950.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B21" s="2">
-        <v>880.0</v>
+        <v>940.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2">
-        <v>840.0</v>
+        <v>930.0</v>
       </c>
     </row>
     <row r="23">
@@ -6026,7 +6143,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>800.0</v>
+        <v>850.0</v>
       </c>
     </row>
     <row r="24">
@@ -6038,7 +6155,7 @@
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>22300</v>
+        <v>23750</v>
       </c>
     </row>
     <row r="26">
@@ -6047,7 +6164,7 @@
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>1014</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="121">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1522,6 +1522,74 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Ma Rốc</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Canada</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Pháp - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Paraguay</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Brazil - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Na Uy</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Anh </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>- Mexico</t>
+    </r>
+  </si>
+  <si>
     <t>Vua đóng góp</t>
   </si>
   <si>
@@ -1529,6 +1597,9 @@
   </si>
   <si>
     <t>Ngôi sao hi vọng</t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
   <si>
     <t>SUM</t>
@@ -1891,95 +1962,95 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>1320</v>
+        <v>1420</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>1110</v>
+        <v>1160</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>1050</v>
+        <v>1150</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1450</v>
+        <v>1550</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>1190</v>
+        <v>1240</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>1090</v>
+        <v>1190</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>980</v>
+        <v>1080</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>970</v>
+        <v>1170</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>1120</v>
+        <v>1220</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>1230</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>1210</v>
+        <v>1360</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>940</v>
+        <v>990</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>1010</v>
+        <v>1110</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>950</v>
+        <v>1050</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>1090</v>
+        <v>1240</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>930</v>
+        <v>1080</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>1060</v>
+        <v>1160</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
@@ -5819,31 +5890,183 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="10"/>
+      <c r="A91" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B91" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F91" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K91" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L91" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O91" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q91" s="7">
+        <v>-50.0</v>
+      </c>
       <c r="X91" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10"/>
+      <c r="A92" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C92" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E92" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F92" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K92" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M92" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N92" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O92" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q92" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T92" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="U92" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X92" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="10"/>
+      <c r="A93" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="H93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="I93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="U93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V93" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W93" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X93" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="10"/>
+      <c r="A94" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="C94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="H94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="U94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V94" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W94" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X94" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="95">
@@ -5956,13 +6179,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2">
@@ -5975,167 +6198,190 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>1450.0</v>
-      </c>
+        <v>1550.0</v>
+      </c>
+      <c r="C2" s="12"/>
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>1320.0</v>
-      </c>
+        <v>1420.0</v>
+      </c>
+      <c r="C3" s="12"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>1250.0</v>
-      </c>
+        <v>1360.0</v>
+      </c>
+      <c r="C4" s="12"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>1210.0</v>
-      </c>
+        <v>1350.0</v>
+      </c>
+      <c r="C5" s="12"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>1190.0</v>
-      </c>
+        <v>1240.0</v>
+      </c>
+      <c r="C6" s="12"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2">
-        <v>1120.0</v>
-      </c>
+        <v>1240.0</v>
+      </c>
+      <c r="C7" s="12"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2">
-        <v>1110.0</v>
-      </c>
+        <v>1230.0</v>
+      </c>
+      <c r="C8" s="12"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="2">
-        <v>1100.0</v>
-      </c>
+        <v>1220.0</v>
+      </c>
+      <c r="C9" s="12"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>1090.0</v>
-      </c>
+        <v>1200.0</v>
+      </c>
+      <c r="C10" s="12"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
-        <v>1090.0</v>
-      </c>
+        <v>1190.0</v>
+      </c>
+      <c r="C11" s="12"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2">
-        <v>1080.0</v>
-      </c>
+        <v>1170.0</v>
+      </c>
+      <c r="C12" s="12"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B13" s="2">
-        <v>1060.0</v>
-      </c>
+        <v>1160.0</v>
+      </c>
+      <c r="C13" s="12"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B14" s="2">
-        <v>1050.0</v>
-      </c>
+        <v>1160.0</v>
+      </c>
+      <c r="C14" s="12"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B15" s="2">
-        <v>1010.0</v>
-      </c>
+        <v>1150.0</v>
+      </c>
+      <c r="C15" s="12"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>1000.0</v>
-      </c>
+        <v>1110.0</v>
+      </c>
+      <c r="C16" s="12"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>1000.0</v>
-      </c>
+        <v>1100.0</v>
+      </c>
+      <c r="C17" s="12"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2">
-        <v>980.0</v>
-      </c>
+        <v>1100.0</v>
+      </c>
+      <c r="C18" s="12"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" s="2">
-        <v>970.0</v>
-      </c>
+        <v>1080.0</v>
+      </c>
+      <c r="C19" s="12"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>950.0</v>
-      </c>
+        <v>1080.0</v>
+      </c>
+      <c r="C20" s="12"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>940.0</v>
-      </c>
+        <v>1050.0</v>
+      </c>
+      <c r="C21" s="12"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2">
-        <v>930.0</v>
+        <v>990.0</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="23">
@@ -6143,28 +6389,29 @@
         <v>7</v>
       </c>
       <c r="B23" s="2">
-        <v>850.0</v>
-      </c>
+        <v>900.0</v>
+      </c>
+      <c r="C23" s="12"/>
     </row>
     <row r="24">
       <c r="A24" s="13"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>23750</v>
+        <v>26050</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>1080</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet state="visible" name="Detail" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Summary" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Ngôi sao" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="124">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1590,16 +1591,53 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Tây Ban Nha</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Bồ Đào Nha</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Bỉ</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Mỹ</t>
+    </r>
+  </si>
+  <si>
+    <t>Argentina - Ai Cập</t>
+  </si>
+  <si>
+    <t>Colombia - Thuỵ Sĩ</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
     <t>Vua đóng góp</t>
   </si>
   <si>
     <t>Góp gạo</t>
-  </si>
-  <si>
-    <t>Ngôi sao hi vọng</t>
-  </si>
-  <si>
-    <t>*</t>
   </si>
   <si>
     <t>SUM</t>
@@ -1748,6 +1786,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1962,27 +2004,27 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>1420</v>
+        <v>1520</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>1160</v>
+        <v>1210</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>1240</v>
+        <v>1340</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -1990,23 +2032,23 @@
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>1180</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>1170</v>
+        <v>1220</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>1220</v>
+        <v>1270</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
@@ -2018,23 +2060,23 @@
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>990</v>
+        <v>1040</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>1110</v>
+        <v>1210</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>1240</v>
+        <v>1290</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
@@ -2042,15 +2084,15 @@
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>1160</v>
+        <v>1310</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2">
@@ -6070,28 +6112,114 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="10"/>
+      <c r="A95" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B95" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F95" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G95" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="I95" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="J95" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P95" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R95" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V95" s="7">
+        <v>100.0</v>
+      </c>
       <c r="X95" s="2">
         <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="C96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="D96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="I96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W96" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="X96" s="2">
+        <f t="shared" si="2"/>
+        <v>850</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="X97" s="2">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="10"/>
-      <c r="X96" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10"/>
-      <c r="X97" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="98">
-      <c r="A98" s="10"/>
+      <c r="A98" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P98" s="7" t="s">
+        <v>119</v>
+      </c>
       <c r="X98" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6174,19 +6302,17 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="17.5"/>
     <col customWidth="1" min="2" max="2" width="20.88"/>
-    <col customWidth="1" min="3" max="3" width="24.38"/>
+    <col customWidth="1" min="3" max="3" width="13.5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>117</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C1" s="11"/>
     </row>
     <row r="2">
       <c r="A2" s="12" t="str">
@@ -6198,7 +6324,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>1550.0</v>
+        <v>1600.0</v>
       </c>
       <c r="C2" s="12"/>
     </row>
@@ -6207,25 +6333,25 @@
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>1420.0</v>
+        <v>1520.0</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
-        <v>1360.0</v>
+        <v>1400.0</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2">
-        <v>1350.0</v>
+        <v>1360.0</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -6234,25 +6360,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>1240.0</v>
+        <v>1340.0</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2">
-        <v>1240.0</v>
+        <v>1310.0</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2">
-        <v>1230.0</v>
+        <v>1290.0</v>
       </c>
       <c r="C8" s="12"/>
     </row>
@@ -6261,7 +6387,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2">
-        <v>1220.0</v>
+        <v>1270.0</v>
       </c>
       <c r="C9" s="12"/>
     </row>
@@ -6270,16 +6396,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>1200.0</v>
+        <v>1250.0</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2">
-        <v>1190.0</v>
+        <v>1230.0</v>
       </c>
       <c r="C11" s="12"/>
     </row>
@@ -6288,7 +6414,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="2">
-        <v>1170.0</v>
+        <v>1220.0</v>
       </c>
       <c r="C12" s="12"/>
     </row>
@@ -6297,16 +6423,16 @@
         <v>2</v>
       </c>
       <c r="B13" s="2">
-        <v>1160.0</v>
+        <v>1210.0</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
-        <v>1160.0</v>
+        <v>1210.0</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -6315,81 +6441,79 @@
         <v>3</v>
       </c>
       <c r="B15" s="2">
-        <v>1150.0</v>
+        <v>1200.0</v>
       </c>
       <c r="C15" s="12"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>1110.0</v>
+        <v>1200.0</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B17" s="2">
-        <v>1100.0</v>
+        <v>1190.0</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2">
-        <v>1100.0</v>
+        <v>1180.0</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>1080.0</v>
+        <v>1150.0</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2">
-        <v>1080.0</v>
+        <v>1100.0</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>1050.0</v>
+        <v>1080.0</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B22" s="2">
-        <v>990.0</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>118</v>
-      </c>
+        <v>1050.0</v>
+      </c>
+      <c r="C22" s="13"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B23" s="2">
-        <v>900.0</v>
+        <v>1040.0</v>
       </c>
       <c r="C23" s="12"/>
     </row>
@@ -6398,20 +6522,20 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>26050</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>1184</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="27">
@@ -6427,6 +6551,42 @@
     </row>
     <row r="30">
       <c r="A30" s="12"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="7">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="7">
+        <v>1.0</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="123">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1625,13 +1625,34 @@
     </r>
   </si>
   <si>
-    <t>Argentina - Ai Cập</t>
-  </si>
-  <si>
-    <t>Colombia - Thuỵ Sĩ</t>
-  </si>
-  <si>
-    <t>*</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Argentina - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Ai Cập</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Colombia - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Thuỵ Sĩ</t>
+    </r>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -2012,7 +2033,7 @@
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>1210</v>
+        <v>1260</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
@@ -2020,11 +2041,11 @@
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>1340</v>
+        <v>1390</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -2032,35 +2053,35 @@
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>1180</v>
+        <v>1230</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>1220</v>
+        <v>1270</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>1270</v>
+        <v>1370</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>1230</v>
+        <v>1280</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>1360</v>
+        <v>1460</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
@@ -2068,31 +2089,31 @@
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>1210</v>
+        <v>1260</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>1290</v>
+        <v>1340</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>1130</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>1310</v>
+        <v>1360</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
@@ -6208,21 +6229,81 @@
       <c r="A97" s="6" t="s">
         <v>117</v>
       </c>
+      <c r="D97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="I97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="U97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V97" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W97" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X97" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="P98" s="7" t="s">
-        <v>119</v>
+      <c r="G98" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L98" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O98" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P98" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R98" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S98" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W98" s="7">
+        <v>50.0</v>
       </c>
       <c r="X98" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="99">
@@ -6307,10 +6388,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="C1" s="11"/>
     </row>
@@ -6324,7 +6405,7 @@
         <v>Tiến Tùng</v>
       </c>
       <c r="B2" s="2">
-        <v>1600.0</v>
+        <v>1650.0</v>
       </c>
       <c r="C2" s="12"/>
     </row>
@@ -6342,7 +6423,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="2">
-        <v>1400.0</v>
+        <v>1500.0</v>
       </c>
       <c r="C4" s="12"/>
     </row>
@@ -6351,7 +6432,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="2">
-        <v>1360.0</v>
+        <v>1460.0</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -6360,34 +6441,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>1340.0</v>
+        <v>1390.0</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2">
-        <v>1310.0</v>
+        <v>1370.0</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>1290.0</v>
+        <v>1360.0</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2">
-        <v>1270.0</v>
+        <v>1340.0</v>
       </c>
       <c r="C9" s="12"/>
     </row>
@@ -6396,79 +6477,79 @@
         <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>1250.0</v>
+        <v>1300.0</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2">
-        <v>1230.0</v>
+        <v>1300.0</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>1220.0</v>
+        <v>1280.0</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2">
-        <v>1210.0</v>
+        <v>1270.0</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B14" s="2">
-        <v>1210.0</v>
+        <v>1260.0</v>
       </c>
       <c r="C14" s="12"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>1200.0</v>
+        <v>1260.0</v>
       </c>
       <c r="C15" s="12"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2">
-        <v>1200.0</v>
+        <v>1230.0</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2">
-        <v>1190.0</v>
+        <v>1200.0</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B18" s="2">
-        <v>1180.0</v>
+        <v>1190.0</v>
       </c>
       <c r="C18" s="12"/>
     </row>
@@ -6486,7 +6567,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="2">
-        <v>1100.0</v>
+        <v>1150.0</v>
       </c>
       <c r="C20" s="12"/>
     </row>
@@ -6495,7 +6576,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>1080.0</v>
+        <v>1130.0</v>
       </c>
       <c r="C21" s="12"/>
     </row>
@@ -6504,7 +6585,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="2">
-        <v>1050.0</v>
+        <v>1100.0</v>
       </c>
       <c r="C22" s="13"/>
     </row>
@@ -6522,20 +6603,20 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B2:B23)</f>
-        <v>27400</v>
+        <v>28450</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B26" s="15">
         <f>ROUND(B25/22,0)</f>
-        <v>1245</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="127">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1653,6 +1653,32 @@
       </rPr>
       <t>Thuỵ Sĩ</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Pháp</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Ma Rốc</t>
+    </r>
+  </si>
+  <si>
+    <t>Tây Ban Nha - Bỉ</t>
+  </si>
+  <si>
+    <t>Anh - Na Uy</t>
+  </si>
+  <si>
+    <t>Argentina - Thuỵ Sĩ</t>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1748,7 +1774,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1778,6 +1804,7 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -2025,19 +2052,19 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>1520</v>
+        <v>1570</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>1260</v>
+        <v>1310</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
@@ -2053,23 +2080,23 @@
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>1230</v>
+        <v>1280</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>1270</v>
+        <v>1320</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>1370</v>
+        <v>1420</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
@@ -2081,15 +2108,15 @@
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>1040</v>
+        <v>1090</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>1260</v>
+        <v>1310</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
@@ -2097,15 +2124,15 @@
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>1340</v>
+        <v>1390</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>1130</v>
+        <v>1180</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>1360</v>
+        <v>1410</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
@@ -2113,7 +2140,7 @@
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
@@ -6307,28 +6334,81 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="10"/>
+      <c r="A99" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="C99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="D99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="I99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="U99" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V99" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X99" s="2">
         <f t="shared" si="2"/>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="X100" s="2">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="10"/>
-      <c r="X100" s="2">
+    <row r="101">
+      <c r="A101" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="X101" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="10"/>
-      <c r="X101" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="102">
-      <c r="A102" s="10"/>
+      <c r="A102" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="X102" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6363,7 +6443,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="10"/>
+      <c r="A107" s="11"/>
       <c r="X107" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6387,16 +6467,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="11"/>
+      <c r="A1" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="12"/>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="str">
+      <c r="A2" s="13" t="str">
         <f t="array" ref="A2:B23">SORT(
 TRANSPOSE({Detail!B2:W2;Detail!B1:W1}),
 2,
@@ -6407,231 +6487,231 @@
       <c r="B2" s="2">
         <v>1650.0</v>
       </c>
-      <c r="C2" s="12"/>
+      <c r="C2" s="13"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>1520.0</v>
-      </c>
-      <c r="C3" s="12"/>
+        <v>1570.0</v>
+      </c>
+      <c r="C3" s="13"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="2">
         <v>1500.0</v>
       </c>
-      <c r="C4" s="12"/>
+      <c r="C4" s="13"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="2">
         <v>1460.0</v>
       </c>
-      <c r="C5" s="12"/>
+      <c r="C5" s="13"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1420.0</v>
+      </c>
+      <c r="C6" s="13"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1410.0</v>
+      </c>
+      <c r="C7" s="13"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B8" s="2">
         <v>1390.0</v>
       </c>
-      <c r="C6" s="12"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1370.0</v>
-      </c>
-      <c r="C7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1360.0</v>
-      </c>
-      <c r="C8" s="12"/>
+      <c r="C8" s="13"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="2">
-        <v>1340.0</v>
-      </c>
-      <c r="C9" s="12"/>
+        <v>1390.0</v>
+      </c>
+      <c r="C9" s="13"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>1300.0</v>
-      </c>
-      <c r="C10" s="12"/>
+        <v>1350.0</v>
+      </c>
+      <c r="C10" s="13"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="2">
-        <v>1300.0</v>
-      </c>
-      <c r="C11" s="12"/>
+        <v>1350.0</v>
+      </c>
+      <c r="C11" s="13"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1320.0</v>
+      </c>
+      <c r="C12" s="13"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1310.0</v>
+      </c>
+      <c r="C13" s="13"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1310.0</v>
+      </c>
+      <c r="C14" s="13"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1280.0</v>
+      </c>
+      <c r="C15" s="13"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B16" s="2">
         <v>1280.0</v>
       </c>
-      <c r="C12" s="12"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1270.0</v>
-      </c>
-      <c r="C13" s="12"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1260.0</v>
-      </c>
-      <c r="C14" s="12"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2">
-        <v>1260.0</v>
-      </c>
-      <c r="C15" s="12"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="2">
-        <v>1230.0</v>
-      </c>
-      <c r="C16" s="12"/>
+      <c r="C16" s="13"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="2">
+        <v>1250.0</v>
+      </c>
+      <c r="C17" s="13"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2">
         <v>1200.0</v>
       </c>
-      <c r="C17" s="12"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="s">
+      <c r="C18" s="13"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B19" s="2">
         <v>1190.0</v>
       </c>
-      <c r="C18" s="12"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="C19" s="13"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1180.0</v>
+      </c>
+      <c r="C20" s="13"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="2">
         <v>1150.0</v>
       </c>
-      <c r="C19" s="12"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="s">
+      <c r="C21" s="13"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B22" s="2">
         <v>1150.0</v>
       </c>
-      <c r="C20" s="12"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="2">
-        <v>1130.0</v>
-      </c>
-      <c r="C21" s="12"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1100.0</v>
-      </c>
-      <c r="C22" s="13"/>
+      <c r="C22" s="14"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B23" s="2">
-        <v>1040.0</v>
-      </c>
-      <c r="C23" s="12"/>
+        <v>1090.0</v>
+      </c>
+      <c r="C23" s="13"/>
     </row>
     <row r="24">
-      <c r="A24" s="13"/>
+      <c r="A24" s="14"/>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" s="15">
+      <c r="A25" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="16">
         <f>SUM(B2:B23)</f>
-        <v>28450</v>
+        <v>29200</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="15">
+      <c r="A26" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="16">
         <f>ROUND(B25/22,0)</f>
-        <v>1293</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14"/>
-      <c r="B27" s="16"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="17"/>
     </row>
     <row r="28">
-      <c r="A28" s="14"/>
-      <c r="B28" s="15"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="16"/>
     </row>
     <row r="29">
-      <c r="A29" s="12"/>
+      <c r="A29" s="13"/>
     </row>
     <row r="30">
-      <c r="A30" s="12"/>
+      <c r="A30" s="13"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -1672,7 +1672,21 @@
     </r>
   </si>
   <si>
-    <t>Tây Ban Nha - Bỉ</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Tây Ban Nha </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>- Bỉ</t>
+    </r>
   </si>
   <si>
     <t>Anh - Na Uy</t>
@@ -2052,7 +2066,7 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>1570</v>
+        <v>1620</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
@@ -2064,7 +2078,7 @@
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
@@ -2084,7 +2098,7 @@
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>1280</v>
+        <v>1330</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
@@ -2092,7 +2106,7 @@
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>1420</v>
+        <v>1470</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
@@ -2108,7 +2122,7 @@
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
@@ -2116,7 +2130,7 @@
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>1310</v>
+        <v>1360</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
@@ -2128,7 +2142,7 @@
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>1180</v>
+        <v>1230</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
@@ -2140,7 +2154,7 @@
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
@@ -6391,9 +6405,30 @@
       <c r="A100" s="6" t="s">
         <v>120</v>
       </c>
+      <c r="B100" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E100" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J100" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L100" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P100" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R100" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="U100" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X100" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="101">
@@ -6494,7 +6529,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>1570.0</v>
+        <v>1620.0</v>
       </c>
       <c r="C3" s="13"/>
     </row>
@@ -6509,19 +6544,19 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>1460.0</v>
+        <v>1470.0</v>
       </c>
       <c r="C5" s="13"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
-        <v>1420.0</v>
+        <v>1460.0</v>
       </c>
       <c r="C6" s="13"/>
     </row>
@@ -6536,16 +6571,16 @@
     </row>
     <row r="8">
       <c r="A8" s="13" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2">
-        <v>1390.0</v>
+        <v>1400.0</v>
       </c>
       <c r="C8" s="13"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2">
         <v>1390.0</v>
@@ -6554,100 +6589,100 @@
     </row>
     <row r="10">
       <c r="A10" s="13" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2">
-        <v>1350.0</v>
+        <v>1390.0</v>
       </c>
       <c r="C10" s="13"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2">
-        <v>1350.0</v>
+        <v>1360.0</v>
       </c>
       <c r="C11" s="13"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>1320.0</v>
+        <v>1350.0</v>
       </c>
       <c r="C12" s="13"/>
     </row>
     <row r="13">
       <c r="A13" s="13" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
-        <v>1310.0</v>
+        <v>1330.0</v>
       </c>
       <c r="C13" s="13"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
-        <v>1310.0</v>
+        <v>1320.0</v>
       </c>
       <c r="C14" s="13"/>
     </row>
     <row r="15">
       <c r="A15" s="13" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B15" s="2">
-        <v>1280.0</v>
+        <v>1310.0</v>
       </c>
       <c r="C15" s="13"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B16" s="2">
-        <v>1280.0</v>
+        <v>1300.0</v>
       </c>
       <c r="C16" s="13"/>
     </row>
     <row r="17">
       <c r="A17" s="13" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
-        <v>1250.0</v>
+        <v>1280.0</v>
       </c>
       <c r="C17" s="13"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2">
-        <v>1200.0</v>
+        <v>1230.0</v>
       </c>
       <c r="C18" s="13"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>1190.0</v>
+        <v>1200.0</v>
       </c>
       <c r="C19" s="13"/>
     </row>
     <row r="20">
       <c r="A20" s="13" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B20" s="2">
-        <v>1180.0</v>
+        <v>1190.0</v>
       </c>
       <c r="C20" s="13"/>
     </row>
@@ -6687,7 +6722,7 @@
       </c>
       <c r="B25" s="16">
         <f>SUM(B2:B23)</f>
-        <v>29200</v>
+        <v>29550</v>
       </c>
     </row>
     <row r="26">
@@ -6696,7 +6731,7 @@
       </c>
       <c r="B26" s="16">
         <f>ROUND(B25/22,0)</f>
-        <v>1327</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="27">

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="133">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1689,7 +1689,21 @@
     </r>
   </si>
   <si>
-    <t>Anh - Na Uy</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Anh - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Na Uy</t>
+    </r>
   </si>
   <si>
     <t>Argentina - Thuỵ Sĩ</t>
@@ -1705,13 +1719,34 @@
   </si>
   <si>
     <t>AVG/người</t>
+  </si>
+  <si>
+    <t>Ma Rốc</t>
+  </si>
+  <si>
+    <t>Bồ Đào Nha</t>
+  </si>
+  <si>
+    <t>Anh</t>
+  </si>
+  <si>
+    <t>Na Uy</t>
+  </si>
+  <si>
+    <t>Thuỵ Sĩ</t>
+  </si>
+  <si>
+    <t>Argentina</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d/m"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1743,6 +1778,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15.0"/>
       <color theme="1"/>
@@ -1750,7 +1790,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1781,6 +1821,18 @@
         <bgColor rgb="FF93C47D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -1788,7 +1840,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1817,9 +1869,22 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1831,9 +1896,15 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2070,7 +2141,7 @@
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
@@ -2082,11 +2153,11 @@
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1650</v>
+        <v>1750</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>1390</v>
+        <v>1490</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -2098,7 +2169,7 @@
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>1330</v>
+        <v>1380</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
@@ -2110,7 +2181,7 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
@@ -2118,15 +2189,15 @@
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>1460</v>
+        <v>1510</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>1090</v>
+        <v>1140</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
@@ -2134,7 +2205,7 @@
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
@@ -2142,7 +2213,7 @@
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>1230</v>
+        <v>1180</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
@@ -2150,11 +2221,11 @@
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2">
@@ -2273,7 +2344,7 @@
         <v>20.0</v>
       </c>
       <c r="X3" s="2">
-        <f t="shared" ref="X3:X107" si="2">sum(B3:W3)</f>
+        <f t="shared" ref="X3:X106" si="2">sum(B3:W3)</f>
         <v>220</v>
       </c>
     </row>
@@ -6012,7 +6083,7 @@
       <c r="O91" s="7">
         <v>50.0</v>
       </c>
-      <c r="Q91" s="7">
+      <c r="Q91" s="10">
         <v>-50.0</v>
       </c>
       <c r="X91" s="2">
@@ -6186,7 +6257,7 @@
       <c r="G95" s="7">
         <v>50.0</v>
       </c>
-      <c r="I95" s="7">
+      <c r="I95" s="11">
         <v>100.0</v>
       </c>
       <c r="J95" s="7">
@@ -6198,7 +6269,7 @@
       <c r="R95" s="7">
         <v>50.0</v>
       </c>
-      <c r="V95" s="7">
+      <c r="V95" s="11">
         <v>100.0</v>
       </c>
       <c r="X95" s="2">
@@ -6435,54 +6506,94 @@
       <c r="A101" s="6" t="s">
         <v>121</v>
       </c>
+      <c r="C101" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F101" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="G101" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="J101" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="M101" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="O101" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P101" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q101" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S101" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="U101" s="13">
+        <v>-50.0</v>
+      </c>
+      <c r="W101" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X101" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>550</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
         <v>122</v>
       </c>
+      <c r="C102" s="14"/>
+      <c r="F102" s="14"/>
+      <c r="H102" s="14"/>
+      <c r="I102" s="14"/>
+      <c r="K102" s="14"/>
+      <c r="M102" s="14"/>
+      <c r="N102" s="14"/>
+      <c r="Q102" s="14"/>
+      <c r="R102" s="14"/>
+      <c r="U102" s="14"/>
+      <c r="V102" s="14"/>
       <c r="X102" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="10"/>
+      <c r="A103" s="15"/>
       <c r="X103" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="10"/>
+      <c r="A104" s="15"/>
       <c r="X104" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="10"/>
+      <c r="A105" s="15"/>
       <c r="X105" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="10"/>
+      <c r="A106" s="15"/>
       <c r="X106" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="11"/>
-      <c r="X107" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A107" s="16"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6496,22 +6607,22 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.5"/>
+    <col customWidth="1" min="1" max="1" width="24.0"/>
     <col customWidth="1" min="2" max="2" width="20.88"/>
     <col customWidth="1" min="3" max="3" width="13.5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="12"/>
+      <c r="C1" s="17"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="str">
+      <c r="A2" s="18" t="str">
         <f t="array" ref="A2:B23">SORT(
 TRANSPOSE({Detail!B2:W2;Detail!B1:W1}),
 2,
@@ -6519,234 +6630,235 @@
 )</f>
         <v>Tiến Tùng</v>
       </c>
-      <c r="B2" s="2">
-        <v>1650.0</v>
-      </c>
-      <c r="C2" s="13"/>
+      <c r="B2" s="18">
+        <v>1750.0</v>
+      </c>
+      <c r="C2" s="18"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="18">
         <v>1620.0</v>
       </c>
-      <c r="C3" s="13"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="2">
-        <v>1500.0</v>
-      </c>
-      <c r="C4" s="13"/>
+      <c r="B4" s="18">
+        <v>1550.0</v>
+      </c>
+      <c r="C4" s="18"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="18">
+        <v>1510.0</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18">
+        <v>1490.0</v>
+      </c>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B7" s="18">
         <v>1470.0</v>
       </c>
-      <c r="C5" s="13"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1460.0</v>
-      </c>
-      <c r="C6" s="13"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="s">
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="18">
+        <v>1450.0</v>
+      </c>
+      <c r="C8" s="18"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B9" s="18">
         <v>1410.0</v>
       </c>
-      <c r="C7" s="13"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="C9" s="18"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="18">
         <v>1400.0</v>
       </c>
-      <c r="C8" s="13"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="C10" s="18"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="18">
         <v>1390.0</v>
       </c>
-      <c r="C9" s="13"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1390.0</v>
-      </c>
-      <c r="C10" s="13"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="s">
+      <c r="C11" s="18"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="18">
+        <v>1380.0</v>
+      </c>
+      <c r="C12" s="18"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B13" s="18">
         <v>1360.0</v>
       </c>
-      <c r="C11" s="13"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1350.0</v>
-      </c>
-      <c r="C12" s="13"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1330.0</v>
-      </c>
-      <c r="C13" s="13"/>
+      <c r="C13" s="18"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="18">
         <v>1320.0</v>
       </c>
-      <c r="C14" s="13"/>
+      <c r="C14" s="18"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="18">
         <v>1310.0</v>
       </c>
-      <c r="C15" s="13"/>
+      <c r="C15" s="18"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="18">
         <v>1300.0</v>
       </c>
-      <c r="C16" s="13"/>
+      <c r="C16" s="18"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="18">
         <v>1280.0</v>
       </c>
-      <c r="C17" s="13"/>
+      <c r="C17" s="18"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="18">
+        <v>1250.0</v>
+      </c>
+      <c r="C18" s="18"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="18">
+        <v>1200.0</v>
+      </c>
+      <c r="C19" s="18"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="18">
+        <v>1190.0</v>
+      </c>
+      <c r="C20" s="18"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="2">
-        <v>1230.0</v>
-      </c>
-      <c r="C18" s="13"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="2">
-        <v>1200.0</v>
-      </c>
-      <c r="C19" s="13"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2">
-        <v>1190.0</v>
-      </c>
-      <c r="C20" s="13"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="s">
+      <c r="B21" s="18">
+        <v>1180.0</v>
+      </c>
+      <c r="C21" s="18"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B22" s="18">
         <v>1150.0</v>
       </c>
-      <c r="C21" s="13"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1150.0</v>
-      </c>
-      <c r="C22" s="14"/>
+      <c r="C22" s="19"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="2">
-        <v>1090.0</v>
-      </c>
-      <c r="C23" s="13"/>
+      <c r="B23" s="18">
+        <v>1140.0</v>
+      </c>
+      <c r="C23" s="18"/>
     </row>
     <row r="24">
-      <c r="A24" s="14"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="18"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="21">
         <f>SUM(B2:B23)</f>
-        <v>29550</v>
+        <v>30100</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="21">
         <f>ROUND(B25/22,0)</f>
-        <v>1343</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15"/>
-      <c r="B27" s="17"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="22"/>
     </row>
     <row r="28">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="23"/>
     </row>
     <row r="29">
-      <c r="A29" s="13"/>
+      <c r="A29" s="18"/>
     </row>
     <row r="30">
-      <c r="A30" s="13"/>
+      <c r="A30" s="18"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6761,28 +6873,692 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="24">
+        <v>46207.0</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="7">
+      <c r="C1" s="19">
         <v>1.0</v>
       </c>
+      <c r="D1" s="19" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="24">
+        <v>46209.0</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7">
+      <c r="C2" s="19">
         <v>1.0</v>
       </c>
+      <c r="D2" s="19" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="24">
+        <v>46209.0</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="7">
+      <c r="C3" s="19">
         <v>1.0</v>
       </c>
+      <c r="D3" s="19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="18"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="18"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="18"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="18"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="18"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="18"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="18"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="18"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="18"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="18"/>
+      <c r="B90" s="18"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="18"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="18"/>
+      <c r="B91" s="18"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="18"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="18"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="18"/>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="18"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="18"/>
+      <c r="D94" s="18"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="18"/>
+      <c r="B95" s="18"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="18"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="18"/>
+      <c r="B96" s="18"/>
+      <c r="C96" s="18"/>
+      <c r="D96" s="18"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="18"/>
+      <c r="B97" s="18"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="18"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="18"/>
+      <c r="B98" s="18"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="18"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -1706,7 +1706,21 @@
     </r>
   </si>
   <si>
-    <t>Argentina - Thuỵ Sĩ</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Argentina - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Thuỵ Sĩ</t>
+    </r>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1840,7 +1854,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1881,7 +1895,6 @@
     <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2141,11 +2154,11 @@
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>1310</v>
+        <v>1360</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
@@ -2153,7 +2166,7 @@
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1750</v>
+        <v>1850</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
@@ -2161,19 +2174,19 @@
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>1190</v>
+        <v>1290</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>1150</v>
+        <v>1250</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>1380</v>
+        <v>1430</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>1320</v>
+        <v>1420</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
@@ -2181,51 +2194,51 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>1280</v>
+        <v>1380</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>1510</v>
+        <v>1560</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>1140</v>
+        <v>1240</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>1360</v>
+        <v>1460</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>1390</v>
+        <v>1440</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>1180</v>
+        <v>1130</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>1410</v>
+        <v>1510</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
@@ -6548,52 +6561,95 @@
       <c r="A102" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C102" s="14"/>
-      <c r="F102" s="14"/>
-      <c r="H102" s="14"/>
-      <c r="I102" s="14"/>
-      <c r="K102" s="14"/>
-      <c r="M102" s="14"/>
-      <c r="N102" s="14"/>
-      <c r="Q102" s="14"/>
-      <c r="R102" s="14"/>
-      <c r="U102" s="14"/>
-      <c r="V102" s="14"/>
+      <c r="C102" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="D102" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="F102" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="H102" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="I102" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="J102" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K102" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="M102" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="N102" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="O102" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P102" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q102" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="R102" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="S102" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T102" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="U102" s="13">
+        <v>-50.0</v>
+      </c>
+      <c r="V102" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="W102" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X102" s="2">
         <f t="shared" si="2"/>
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="14"/>
+      <c r="X103" s="2">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="15"/>
-      <c r="X103" s="2">
+    <row r="104">
+      <c r="A104" s="14"/>
+      <c r="X104" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="15"/>
-      <c r="X104" s="2">
+    <row r="105">
+      <c r="A105" s="14"/>
+      <c r="X105" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="15"/>
-      <c r="X105" s="2">
+    <row r="106">
+      <c r="A106" s="14"/>
+      <c r="X106" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="15"/>
-      <c r="X106" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="107">
-      <c r="A107" s="16"/>
+      <c r="A107" s="15"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6613,16 +6669,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="17"/>
+      <c r="C1" s="16"/>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="str">
+      <c r="A2" s="17" t="str">
         <f t="array" ref="A2:B23">SORT(
 TRANSPOSE({Detail!B2:W2;Detail!B1:W1}),
 2,
@@ -6630,235 +6686,235 @@
 )</f>
         <v>Tiến Tùng</v>
       </c>
-      <c r="B2" s="18">
-        <v>1750.0</v>
-      </c>
-      <c r="C2" s="18"/>
+      <c r="B2" s="17">
+        <v>1850.0</v>
+      </c>
+      <c r="C2" s="17"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="17">
         <v>1620.0</v>
       </c>
-      <c r="C3" s="18"/>
+      <c r="C3" s="17"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="18">
-        <v>1550.0</v>
-      </c>
-      <c r="C4" s="18"/>
+      <c r="B4" s="17">
+        <v>1600.0</v>
+      </c>
+      <c r="C4" s="17"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="17">
+        <v>1560.0</v>
+      </c>
+      <c r="C5" s="17"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="17">
         <v>1510.0</v>
       </c>
-      <c r="C5" s="18"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="s">
+      <c r="C6" s="17"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="17">
+        <v>1500.0</v>
+      </c>
+      <c r="C7" s="17"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="17">
+        <v>1500.0</v>
+      </c>
+      <c r="C8" s="17"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B9" s="17">
         <v>1490.0</v>
       </c>
-      <c r="C6" s="18"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="C9" s="17"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B10" s="17">
         <v>1470.0</v>
       </c>
-      <c r="C7" s="18"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="18">
-        <v>1450.0</v>
-      </c>
-      <c r="C8" s="18"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="18">
-        <v>1410.0</v>
-      </c>
-      <c r="C9" s="18"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="18">
-        <v>1400.0</v>
-      </c>
-      <c r="C10" s="18"/>
+      <c r="C10" s="17"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="17">
+        <v>1460.0</v>
+      </c>
+      <c r="C11" s="17"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="18">
-        <v>1390.0</v>
-      </c>
-      <c r="C11" s="18"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="s">
+      <c r="B12" s="17">
+        <v>1440.0</v>
+      </c>
+      <c r="C12" s="17"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B13" s="17">
+        <v>1430.0</v>
+      </c>
+      <c r="C13" s="17"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="17">
+        <v>1420.0</v>
+      </c>
+      <c r="C14" s="17"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="17">
         <v>1380.0</v>
       </c>
-      <c r="C12" s="18"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="18">
+      <c r="C15" s="17"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="17">
         <v>1360.0</v>
       </c>
-      <c r="C13" s="18"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="18">
-        <v>1320.0</v>
-      </c>
-      <c r="C14" s="18"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="18">
-        <v>1310.0</v>
-      </c>
-      <c r="C15" s="18"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="s">
+      <c r="C16" s="17"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="17">
+        <v>1350.0</v>
+      </c>
+      <c r="C17" s="17"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B18" s="17">
         <v>1300.0</v>
       </c>
-      <c r="C16" s="18"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="18">
-        <v>1280.0</v>
-      </c>
-      <c r="C17" s="18"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="18">
+      <c r="C18" s="17"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="17">
+        <v>1290.0</v>
+      </c>
+      <c r="C19" s="17"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="17">
         <v>1250.0</v>
       </c>
-      <c r="C18" s="18"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="s">
+      <c r="C20" s="17"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="18">
-        <v>1200.0</v>
-      </c>
-      <c r="C19" s="18"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="18">
-        <v>1190.0</v>
-      </c>
-      <c r="C20" s="18"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="s">
+      <c r="B21" s="17">
+        <v>1250.0</v>
+      </c>
+      <c r="C21" s="17"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="17">
+        <v>1240.0</v>
+      </c>
+      <c r="C22" s="18"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="18">
-        <v>1180.0</v>
-      </c>
-      <c r="C21" s="18"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="18">
-        <v>1150.0</v>
-      </c>
-      <c r="C22" s="19"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="18">
-        <v>1140.0</v>
-      </c>
-      <c r="C23" s="18"/>
+      <c r="B23" s="17">
+        <v>1130.0</v>
+      </c>
+      <c r="C23" s="17"/>
     </row>
     <row r="24">
-      <c r="A24" s="19"/>
-      <c r="B24" s="18"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="17"/>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="20">
         <f>SUM(B2:B23)</f>
-        <v>30100</v>
+        <v>31400</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="20">
         <f>ROUND(B25/22,0)</f>
-        <v>1368</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20"/>
-      <c r="B27" s="22"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="21"/>
     </row>
     <row r="28">
-      <c r="A28" s="20"/>
-      <c r="B28" s="23"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="22"/>
     </row>
     <row r="29">
-      <c r="A29" s="18"/>
+      <c r="A29" s="17"/>
     </row>
     <row r="30">
-      <c r="A30" s="18"/>
+      <c r="A30" s="17"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6873,692 +6929,692 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24">
+      <c r="A1" s="23">
         <v>46207.0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="19">
+      <c r="C1" s="18">
         <v>1.0</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24">
+      <c r="A2" s="23">
         <v>46209.0</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="18">
         <v>1.0</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24">
+      <c r="A3" s="23">
         <v>46209.0</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="18">
         <v>1.0</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24">
+      <c r="A4" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="18">
         <v>1.0</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24">
+      <c r="A5" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="18">
         <v>1.0</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24">
+      <c r="A6" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="18">
         <v>1.0</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24">
+      <c r="A7" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="18">
         <v>1.0</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24">
+      <c r="A8" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="18">
         <v>1.0</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24">
+      <c r="A9" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="18">
         <v>1.0</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24">
+      <c r="A10" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="18">
         <v>1.0</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24">
+      <c r="A11" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="18">
         <v>1.0</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24">
+      <c r="A12" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="18">
         <v>1.0</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24">
+      <c r="A13" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="18">
         <v>1.0</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24">
+      <c r="A14" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <v>1.0</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24">
+      <c r="A15" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="18">
         <v>1.0</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24">
+      <c r="A16" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="18">
         <v>1.0</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24">
+      <c r="A17" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="18">
         <v>1.0</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
     </row>
     <row r="25">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
     </row>
     <row r="26">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
     </row>
     <row r="27">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
     </row>
     <row r="28">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
     </row>
     <row r="29">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
     </row>
     <row r="30">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
     </row>
     <row r="31">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
     </row>
     <row r="32">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
     </row>
     <row r="33">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
     </row>
     <row r="34">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
     </row>
     <row r="35">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
     </row>
     <row r="36">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
     </row>
     <row r="37">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
     </row>
     <row r="38">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
     </row>
     <row r="39">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
     </row>
     <row r="40">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
     </row>
     <row r="41">
-      <c r="A41" s="18"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
     </row>
     <row r="42">
-      <c r="A42" s="18"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
     </row>
     <row r="43">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
     </row>
     <row r="44">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
     </row>
     <row r="45">
-      <c r="A45" s="18"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
     </row>
     <row r="46">
-      <c r="A46" s="18"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
     </row>
     <row r="47">
-      <c r="A47" s="18"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
     </row>
     <row r="48">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
     </row>
     <row r="49">
-      <c r="A49" s="18"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
     </row>
     <row r="50">
-      <c r="A50" s="18"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
     </row>
     <row r="51">
-      <c r="A51" s="18"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
     </row>
     <row r="52">
-      <c r="A52" s="18"/>
-      <c r="B52" s="18"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="18"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
     </row>
     <row r="53">
-      <c r="A53" s="18"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
     </row>
     <row r="54">
-      <c r="A54" s="18"/>
-      <c r="B54" s="18"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
     </row>
     <row r="55">
-      <c r="A55" s="18"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
     </row>
     <row r="56">
-      <c r="A56" s="18"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
     </row>
     <row r="57">
-      <c r="A57" s="18"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
+      <c r="A57" s="17"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
     </row>
     <row r="58">
-      <c r="A58" s="18"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
+      <c r="A58" s="17"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
     </row>
     <row r="59">
-      <c r="A59" s="18"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
     </row>
     <row r="60">
-      <c r="A60" s="18"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
     </row>
     <row r="61">
-      <c r="A61" s="18"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
     </row>
     <row r="62">
-      <c r="A62" s="18"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
     </row>
     <row r="63">
-      <c r="A63" s="18"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
     </row>
     <row r="64">
-      <c r="A64" s="18"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
     </row>
     <row r="65">
-      <c r="A65" s="18"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
+      <c r="A65" s="17"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
     </row>
     <row r="66">
-      <c r="A66" s="18"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
     </row>
     <row r="67">
-      <c r="A67" s="18"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="18"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
     </row>
     <row r="68">
-      <c r="A68" s="18"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
     </row>
     <row r="69">
-      <c r="A69" s="18"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
     </row>
     <row r="70">
-      <c r="A70" s="18"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
+      <c r="A70" s="17"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
     </row>
     <row r="71">
-      <c r="A71" s="18"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
     </row>
     <row r="72">
-      <c r="A72" s="18"/>
-      <c r="B72" s="18"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
+      <c r="A72" s="17"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
     </row>
     <row r="73">
-      <c r="A73" s="18"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
+      <c r="A73" s="17"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="17"/>
     </row>
     <row r="74">
-      <c r="A74" s="18"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
     </row>
     <row r="75">
-      <c r="A75" s="18"/>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
     </row>
     <row r="76">
-      <c r="A76" s="18"/>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17"/>
     </row>
     <row r="77">
-      <c r="A77" s="18"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
+      <c r="A77" s="17"/>
+      <c r="B77" s="17"/>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
     </row>
     <row r="78">
-      <c r="A78" s="18"/>
-      <c r="B78" s="18"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="18"/>
+      <c r="A78" s="17"/>
+      <c r="B78" s="17"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
     </row>
     <row r="79">
-      <c r="A79" s="18"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
+      <c r="A79" s="17"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
     </row>
     <row r="80">
-      <c r="A80" s="18"/>
-      <c r="B80" s="18"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
     </row>
     <row r="81">
-      <c r="A81" s="18"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
+      <c r="A81" s="17"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
     </row>
     <row r="82">
-      <c r="A82" s="18"/>
-      <c r="B82" s="18"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="18"/>
+      <c r="A82" s="17"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="17"/>
     </row>
     <row r="83">
-      <c r="A83" s="18"/>
-      <c r="B83" s="18"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="18"/>
+      <c r="A83" s="17"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
     </row>
     <row r="84">
-      <c r="A84" s="18"/>
-      <c r="B84" s="18"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="18"/>
+      <c r="A84" s="17"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
     </row>
     <row r="85">
-      <c r="A85" s="18"/>
-      <c r="B85" s="18"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
+      <c r="A85" s="17"/>
+      <c r="B85" s="17"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="17"/>
     </row>
     <row r="86">
-      <c r="A86" s="18"/>
-      <c r="B86" s="18"/>
-      <c r="C86" s="18"/>
-      <c r="D86" s="18"/>
+      <c r="A86" s="17"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="17"/>
     </row>
     <row r="87">
-      <c r="A87" s="18"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
+      <c r="A87" s="17"/>
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="17"/>
     </row>
     <row r="88">
-      <c r="A88" s="18"/>
-      <c r="B88" s="18"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
+      <c r="A88" s="17"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="17"/>
     </row>
     <row r="89">
-      <c r="A89" s="18"/>
-      <c r="B89" s="18"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
+      <c r="A89" s="17"/>
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
     </row>
     <row r="90">
-      <c r="A90" s="18"/>
-      <c r="B90" s="18"/>
-      <c r="C90" s="18"/>
-      <c r="D90" s="18"/>
+      <c r="A90" s="17"/>
+      <c r="B90" s="17"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="17"/>
     </row>
     <row r="91">
-      <c r="A91" s="18"/>
-      <c r="B91" s="18"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="18"/>
+      <c r="A91" s="17"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="17"/>
     </row>
     <row r="92">
-      <c r="A92" s="18"/>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="18"/>
+      <c r="A92" s="17"/>
+      <c r="B92" s="17"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17"/>
     </row>
     <row r="93">
-      <c r="A93" s="18"/>
-      <c r="B93" s="18"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18"/>
+      <c r="A93" s="17"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17"/>
     </row>
     <row r="94">
-      <c r="A94" s="18"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="18"/>
-      <c r="D94" s="18"/>
+      <c r="A94" s="17"/>
+      <c r="B94" s="17"/>
+      <c r="C94" s="17"/>
+      <c r="D94" s="17"/>
     </row>
     <row r="95">
-      <c r="A95" s="18"/>
-      <c r="B95" s="18"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="18"/>
+      <c r="A95" s="17"/>
+      <c r="B95" s="17"/>
+      <c r="C95" s="17"/>
+      <c r="D95" s="17"/>
     </row>
     <row r="96">
-      <c r="A96" s="18"/>
-      <c r="B96" s="18"/>
-      <c r="C96" s="18"/>
-      <c r="D96" s="18"/>
+      <c r="A96" s="17"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="17"/>
     </row>
     <row r="97">
-      <c r="A97" s="18"/>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
+      <c r="A97" s="17"/>
+      <c r="B97" s="17"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="17"/>
     </row>
     <row r="98">
-      <c r="A98" s="18"/>
-      <c r="B98" s="18"/>
-      <c r="C98" s="18"/>
-      <c r="D98" s="18"/>
+      <c r="A98" s="17"/>
+      <c r="B98" s="17"/>
+      <c r="C98" s="17"/>
+      <c r="D98" s="17"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="139">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1723,6 +1723,46 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Pháp - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Tây Ban Nha</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Arrgentina</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> - Anh</t>
+    </r>
+  </si>
+  <si>
+    <t>Pháp - Anh</t>
+  </si>
+  <si>
+    <t>Tây Ban Nha - Argentina</t>
+  </si>
+  <si>
     <t>Vua đóng góp</t>
   </si>
   <si>
@@ -1751,6 +1791,12 @@
   </si>
   <si>
     <t>Argentina</t>
+  </si>
+  <si>
+    <t>Thanh Quanh</t>
+  </si>
+  <si>
+    <t>Tây Ban Nha</t>
   </si>
 </sst>
 </file>
@@ -1895,7 +1941,6 @@
     <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -1905,6 +1950,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -2150,11 +2198,11 @@
     <row r="1">
       <c r="B1" s="1">
         <f t="shared" ref="B1:W1" si="1">sum(B3:B113)</f>
-        <v>1620</v>
+        <v>1670</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="1"/>
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
@@ -2162,7 +2210,7 @@
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
@@ -2170,7 +2218,7 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>1490</v>
+        <v>1540</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
@@ -2178,19 +2226,19 @@
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>1430</v>
+        <v>1530</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>1420</v>
+        <v>1520</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>1470</v>
+        <v>1570</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
@@ -2198,7 +2246,7 @@
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>1380</v>
+        <v>1480</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
@@ -2206,23 +2254,23 @@
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
-        <v>1240</v>
+        <v>1340</v>
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>1460</v>
+        <v>1510</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>1440</v>
+        <v>1490</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
@@ -2230,7 +2278,7 @@
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>1510</v>
+        <v>1610</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
@@ -2238,7 +2286,7 @@
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2">
@@ -6621,35 +6669,112 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="14"/>
+      <c r="A103" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E103" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G103" s="13">
+        <v>-50.0</v>
+      </c>
+      <c r="J103" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K103" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L103" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N103" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P103" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="R103" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S103" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X103" s="2">
         <f t="shared" si="2"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B104" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="C104" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="E104" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="G104" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="I104" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="J104" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="K104" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L104" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="N104" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="P104" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="Q104" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="S104" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T104" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V104" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="X104" s="2">
+        <f t="shared" si="2"/>
+        <v>850</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="X105" s="2">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="14"/>
-      <c r="X104" s="2">
+    <row r="106">
+      <c r="A106" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="X106" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="14"/>
-      <c r="X105" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="14"/>
-      <c r="X106" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="107">
-      <c r="A107" s="15"/>
+      <c r="A107" s="14"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6669,16 +6794,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="16"/>
+      <c r="A1" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="15"/>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="str">
+      <c r="A2" s="16" t="str">
         <f t="array" ref="A2:B23">SORT(
 TRANSPOSE({Detail!B2:W2;Detail!B1:W1}),
 2,
@@ -6686,220 +6811,220 @@
 )</f>
         <v>Tiến Tùng</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="16">
         <v>1850.0</v>
       </c>
-      <c r="C2" s="17"/>
+      <c r="C2" s="16"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="17">
-        <v>1620.0</v>
-      </c>
-      <c r="C3" s="17"/>
+      <c r="B3" s="16">
+        <v>1670.0</v>
+      </c>
+      <c r="C3" s="16"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="16">
+        <v>1610.0</v>
+      </c>
+      <c r="C4" s="16"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="16">
+        <v>1600.0</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B6" s="16">
         <v>1600.0</v>
       </c>
-      <c r="C4" s="17"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16">
+        <v>1570.0</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B8" s="16">
         <v>1560.0</v>
       </c>
-      <c r="C5" s="17"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="17">
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16">
+        <v>1540.0</v>
+      </c>
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="16">
+        <v>1530.0</v>
+      </c>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="16">
+        <v>1520.0</v>
+      </c>
+      <c r="C11" s="16"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="16">
         <v>1510.0</v>
       </c>
-      <c r="C6" s="17"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B13" s="16">
         <v>1500.0</v>
       </c>
-      <c r="C7" s="17"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="17">
-        <v>1500.0</v>
-      </c>
-      <c r="C8" s="17"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="17">
+      <c r="C13" s="16"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="16">
         <v>1490.0</v>
       </c>
-      <c r="C9" s="17"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="17">
-        <v>1470.0</v>
-      </c>
-      <c r="C10" s="17"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="17">
-        <v>1460.0</v>
-      </c>
-      <c r="C11" s="17"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="17">
-        <v>1440.0</v>
-      </c>
-      <c r="C12" s="17"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="17">
-        <v>1430.0</v>
-      </c>
-      <c r="C13" s="17"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="17">
-        <v>1420.0</v>
-      </c>
-      <c r="C14" s="17"/>
+      <c r="C14" s="16"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="17">
-        <v>1380.0</v>
-      </c>
-      <c r="C15" s="17"/>
+      <c r="B15" s="16">
+        <v>1480.0</v>
+      </c>
+      <c r="C15" s="16"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="16">
+        <v>1400.0</v>
+      </c>
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="16">
+        <v>1400.0</v>
+      </c>
+      <c r="C17" s="16"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B18" s="16">
         <v>1360.0</v>
       </c>
-      <c r="C16" s="17"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="17">
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="16">
         <v>1350.0</v>
       </c>
-      <c r="C17" s="17"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="17">
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="16">
+        <v>1340.0</v>
+      </c>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="16">
         <v>1300.0</v>
       </c>
-      <c r="C18" s="17"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="s">
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B22" s="16">
         <v>1290.0</v>
       </c>
-      <c r="C19" s="17"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="17">
-        <v>1250.0</v>
-      </c>
-      <c r="C20" s="17"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="17">
-        <v>1250.0</v>
-      </c>
-      <c r="C21" s="17"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="17">
-        <v>1240.0</v>
-      </c>
-      <c r="C22" s="18"/>
+      <c r="C22" s="17"/>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="18">
         <v>1130.0</v>
       </c>
-      <c r="C23" s="17"/>
+      <c r="C23" s="16"/>
     </row>
     <row r="24">
-      <c r="A24" s="18"/>
-      <c r="B24" s="17"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B25" s="20">
         <f>SUM(B2:B23)</f>
-        <v>31400</v>
+        <v>32600</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B26" s="20">
         <f>ROUND(B25/22,0)</f>
-        <v>1427</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="27">
@@ -6911,10 +7036,10 @@
       <c r="B28" s="22"/>
     </row>
     <row r="29">
-      <c r="A29" s="17"/>
+      <c r="A29" s="16"/>
     </row>
     <row r="30">
-      <c r="A30" s="17"/>
+      <c r="A30" s="16"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6932,689 +7057,757 @@
       <c r="A1" s="23">
         <v>46207.0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="18">
+      <c r="C1" s="17">
         <v>1.0</v>
       </c>
-      <c r="D1" s="18" t="s">
-        <v>127</v>
+      <c r="D1" s="17" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="23">
         <v>46209.0</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="17">
         <v>1.0</v>
       </c>
-      <c r="D2" s="18" t="s">
-        <v>128</v>
+      <c r="D2" s="17" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="23">
         <v>46209.0</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="17">
         <v>1.0</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>128</v>
+      <c r="D3" s="17" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="17">
         <v>1.0</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>129</v>
+      <c r="D4" s="17" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="17">
         <v>1.0</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>129</v>
+      <c r="D5" s="17" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="17">
         <v>1.0</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>130</v>
+      <c r="D6" s="17" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="17">
         <v>1.0</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>131</v>
+      <c r="D7" s="17" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="17">
         <v>1.0</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>132</v>
+      <c r="D8" s="17" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="17">
         <v>1.0</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>132</v>
+      <c r="D9" s="17" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <v>1.0</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>132</v>
+      <c r="D10" s="17" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <v>1.0</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>132</v>
+      <c r="D11" s="17" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <v>1.0</v>
       </c>
-      <c r="D12" s="18" t="s">
-        <v>132</v>
+      <c r="D12" s="17" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <v>1.0</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>132</v>
+      <c r="D13" s="17" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <v>1.0</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>132</v>
+      <c r="D14" s="17" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="17">
         <v>1.0</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>132</v>
+      <c r="D15" s="17" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="17">
         <v>1.0</v>
       </c>
-      <c r="D16" s="18" t="s">
-        <v>132</v>
+      <c r="D16" s="17" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="23">
         <v>46214.0</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="17">
         <v>1.0</v>
       </c>
-      <c r="D17" s="18" t="s">
-        <v>132</v>
-      </c>
+      <c r="D17" s="17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23">
+        <v>46217.0</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23">
+        <v>46218.0</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23">
+        <v>46218.0</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23">
+        <v>46218.0</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="23"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
     </row>
     <row r="24">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
     </row>
     <row r="25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
     </row>
     <row r="26">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
     </row>
     <row r="27">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
     </row>
     <row r="28">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
     </row>
     <row r="29">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
     </row>
     <row r="30">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
     </row>
     <row r="31">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
     </row>
     <row r="32">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
     </row>
     <row r="33">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
     </row>
     <row r="34">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
     </row>
     <row r="35">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
     </row>
     <row r="36">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
     </row>
     <row r="37">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
     </row>
     <row r="38">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
     </row>
     <row r="39">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
+      <c r="A39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
     </row>
     <row r="40">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
+      <c r="A40" s="16"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
     </row>
     <row r="41">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
+      <c r="A41" s="16"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
     </row>
     <row r="42">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
+      <c r="A42" s="16"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
     </row>
     <row r="43">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
+      <c r="A43" s="16"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
     </row>
     <row r="44">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
+      <c r="A44" s="16"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
     </row>
     <row r="45">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
     </row>
     <row r="46">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
     </row>
     <row r="47">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
     </row>
     <row r="48">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
     </row>
     <row r="49">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
+      <c r="A49" s="16"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
     </row>
     <row r="50">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
+      <c r="A50" s="16"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
     </row>
     <row r="51">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
+      <c r="A51" s="16"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
     </row>
     <row r="52">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
+      <c r="A52" s="16"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
     </row>
     <row r="53">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
+      <c r="A53" s="16"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
     </row>
     <row r="54">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
+      <c r="A54" s="16"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
     </row>
     <row r="55">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
+      <c r="A55" s="16"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
     </row>
     <row r="56">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
+      <c r="A56" s="16"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
     </row>
     <row r="57">
-      <c r="A57" s="17"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
+      <c r="A57" s="16"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
     </row>
     <row r="58">
-      <c r="A58" s="17"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
+      <c r="A58" s="16"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
     </row>
     <row r="59">
-      <c r="A59" s="17"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
+      <c r="A59" s="16"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
     </row>
     <row r="60">
-      <c r="A60" s="17"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
+      <c r="A60" s="16"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
     </row>
     <row r="61">
-      <c r="A61" s="17"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="17"/>
+      <c r="A61" s="16"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
     </row>
     <row r="62">
-      <c r="A62" s="17"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
+      <c r="A62" s="16"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
     </row>
     <row r="63">
-      <c r="A63" s="17"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
+      <c r="A63" s="16"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
     </row>
     <row r="64">
-      <c r="A64" s="17"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
+      <c r="A64" s="16"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
     </row>
     <row r="65">
-      <c r="A65" s="17"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
+      <c r="A65" s="16"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
     </row>
     <row r="66">
-      <c r="A66" s="17"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
+      <c r="A66" s="16"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
     </row>
     <row r="67">
-      <c r="A67" s="17"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
+      <c r="A67" s="16"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
     </row>
     <row r="68">
-      <c r="A68" s="17"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
+      <c r="A68" s="16"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
     </row>
     <row r="69">
-      <c r="A69" s="17"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
+      <c r="A69" s="16"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
     </row>
     <row r="70">
-      <c r="A70" s="17"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17"/>
+      <c r="A70" s="16"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
     </row>
     <row r="71">
-      <c r="A71" s="17"/>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
+      <c r="A71" s="16"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
     </row>
     <row r="72">
-      <c r="A72" s="17"/>
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
+      <c r="A72" s="16"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
     </row>
     <row r="73">
-      <c r="A73" s="17"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="17"/>
+      <c r="A73" s="16"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16"/>
     </row>
     <row r="74">
-      <c r="A74" s="17"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="17"/>
-      <c r="D74" s="17"/>
+      <c r="A74" s="16"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
     </row>
     <row r="75">
-      <c r="A75" s="17"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="17"/>
+      <c r="A75" s="16"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
     </row>
     <row r="76">
-      <c r="A76" s="17"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="17"/>
+      <c r="A76" s="16"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
     </row>
     <row r="77">
-      <c r="A77" s="17"/>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
+      <c r="A77" s="16"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
     </row>
     <row r="78">
-      <c r="A78" s="17"/>
-      <c r="B78" s="17"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="17"/>
+      <c r="A78" s="16"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
     </row>
     <row r="79">
-      <c r="A79" s="17"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
+      <c r="A79" s="16"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
     </row>
     <row r="80">
-      <c r="A80" s="17"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
+      <c r="A80" s="16"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
     </row>
     <row r="81">
-      <c r="A81" s="17"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
+      <c r="A81" s="16"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
     </row>
     <row r="82">
-      <c r="A82" s="17"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
+      <c r="A82" s="16"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="16"/>
     </row>
     <row r="83">
-      <c r="A83" s="17"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
+      <c r="A83" s="16"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
     </row>
     <row r="84">
-      <c r="A84" s="17"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
+      <c r="A84" s="16"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
     </row>
     <row r="85">
-      <c r="A85" s="17"/>
-      <c r="B85" s="17"/>
-      <c r="C85" s="17"/>
-      <c r="D85" s="17"/>
+      <c r="A85" s="16"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="16"/>
     </row>
     <row r="86">
-      <c r="A86" s="17"/>
-      <c r="B86" s="17"/>
-      <c r="C86" s="17"/>
-      <c r="D86" s="17"/>
+      <c r="A86" s="16"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16"/>
     </row>
     <row r="87">
-      <c r="A87" s="17"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
+      <c r="A87" s="16"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
     </row>
     <row r="88">
-      <c r="A88" s="17"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17"/>
-      <c r="D88" s="17"/>
+      <c r="A88" s="16"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16"/>
     </row>
     <row r="89">
-      <c r="A89" s="17"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="17"/>
+      <c r="A89" s="16"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="16"/>
     </row>
     <row r="90">
-      <c r="A90" s="17"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="17"/>
-      <c r="D90" s="17"/>
+      <c r="A90" s="16"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
     </row>
     <row r="91">
-      <c r="A91" s="17"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="17"/>
+      <c r="A91" s="16"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="16"/>
     </row>
     <row r="92">
-      <c r="A92" s="17"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17"/>
-      <c r="D92" s="17"/>
+      <c r="A92" s="16"/>
+      <c r="B92" s="16"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="16"/>
     </row>
     <row r="93">
-      <c r="A93" s="17"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="17"/>
+      <c r="A93" s="16"/>
+      <c r="B93" s="16"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="16"/>
     </row>
     <row r="94">
-      <c r="A94" s="17"/>
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
-      <c r="D94" s="17"/>
+      <c r="A94" s="16"/>
+      <c r="B94" s="16"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="16"/>
     </row>
     <row r="95">
-      <c r="A95" s="17"/>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
-      <c r="D95" s="17"/>
+      <c r="A95" s="16"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="16"/>
     </row>
     <row r="96">
-      <c r="A96" s="17"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="17"/>
-      <c r="D96" s="17"/>
+      <c r="A96" s="16"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="16"/>
     </row>
     <row r="97">
-      <c r="A97" s="17"/>
-      <c r="B97" s="17"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="17"/>
+      <c r="A97" s="16"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="16"/>
     </row>
     <row r="98">
-      <c r="A98" s="17"/>
-      <c r="B98" s="17"/>
-      <c r="C98" s="17"/>
-      <c r="D98" s="17"/>
+      <c r="A98" s="16"/>
+      <c r="B98" s="16"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="16"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="141">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1757,7 +1757,21 @@
     </r>
   </si>
   <si>
-    <t>Pháp - Anh</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Pháp - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Anh</t>
+    </r>
   </si>
   <si>
     <t>Tây Ban Nha - Argentina</t>
@@ -1769,6 +1783,9 @@
     <t>Góp gạo</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>SUM</t>
   </si>
   <si>
@@ -1797,6 +1814,9 @@
   </si>
   <si>
     <t>Tây Ban Nha</t>
+  </si>
+  <si>
+    <t>Pháp</t>
   </si>
 </sst>
 </file>
@@ -1850,7 +1870,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1889,6 +1909,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
       </patternFill>
@@ -1900,7 +1926,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1941,6 +1967,9 @@
     <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -1951,7 +1980,7 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2206,7 +2235,7 @@
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>1360</v>
+        <v>1410</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
@@ -2222,15 +2251,15 @@
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>1290</v>
+        <v>1390</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>1530</v>
+        <v>1580</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
@@ -2238,7 +2267,7 @@
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>1570</v>
+        <v>1670</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
@@ -2246,7 +2275,7 @@
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>1480</v>
+        <v>1580</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
@@ -2254,7 +2283,7 @@
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
@@ -2262,31 +2291,31 @@
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>1510</v>
+        <v>1560</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
-        <v>1490</v>
+        <v>1540</v>
       </c>
       <c r="U1" s="1">
         <f t="shared" si="1"/>
-        <v>1130</v>
+        <v>2260</v>
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>1610</v>
+        <v>1660</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2">
@@ -6747,21 +6776,60 @@
       <c r="T104" s="7">
         <v>50.0</v>
       </c>
+      <c r="U104" s="14">
+        <v>1130.0</v>
+      </c>
       <c r="V104" s="12">
         <v>100.0</v>
       </c>
       <c r="X104" s="2">
         <f t="shared" si="2"/>
-        <v>850</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
         <v>125</v>
       </c>
+      <c r="D105" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="H105" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="I105" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="J105" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="L105" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="N105" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="P105" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="R105" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="S105" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="T105" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="V105" s="7">
+        <v>50.0</v>
+      </c>
+      <c r="W105" s="7">
+        <v>50.0</v>
+      </c>
       <c r="X105" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>850</v>
       </c>
     </row>
     <row r="106">
@@ -6774,7 +6842,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="14"/>
+      <c r="A107" s="15"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6794,252 +6862,255 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C1" s="15"/>
+      <c r="C1" s="16"/>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="str">
+      <c r="A2" s="17" t="str">
         <f t="array" ref="A2:B23">SORT(
 TRANSPOSE({Detail!B2:W2;Detail!B1:W1}),
 2,
 FALSE
 )</f>
-        <v>Tiến Tùng</v>
-      </c>
-      <c r="B2" s="16">
+        <v>Chính Đạt</v>
+      </c>
+      <c r="B2" s="17">
+        <v>2260.0</v>
+      </c>
+      <c r="C2" s="17"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="17">
         <v>1850.0</v>
       </c>
-      <c r="C2" s="16"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="s">
+      <c r="C3" s="17"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="17">
+        <v>1700.0</v>
+      </c>
+      <c r="C4" s="17"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B5" s="17">
         <v>1670.0</v>
       </c>
-      <c r="C3" s="16"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="s">
+      <c r="C5" s="17"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="17">
+        <v>1670.0</v>
+      </c>
+      <c r="C6" s="17"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="16">
-        <v>1610.0</v>
-      </c>
-      <c r="C4" s="16"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="16">
-        <v>1600.0</v>
-      </c>
-      <c r="C5" s="16"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="s">
+      <c r="B7" s="17">
+        <v>1660.0</v>
+      </c>
+      <c r="C7" s="17"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="16">
-        <v>1600.0</v>
-      </c>
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="16">
-        <v>1570.0</v>
-      </c>
-      <c r="C7" s="16"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="s">
+      <c r="B8" s="17">
+        <v>1650.0</v>
+      </c>
+      <c r="C8" s="17"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17">
+        <v>1580.0</v>
+      </c>
+      <c r="C9" s="17"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="17">
+        <v>1580.0</v>
+      </c>
+      <c r="C10" s="17"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B11" s="17">
         <v>1560.0</v>
       </c>
-      <c r="C8" s="16"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="s">
+      <c r="C11" s="17"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="17">
+        <v>1560.0</v>
+      </c>
+      <c r="C12" s="17"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B13" s="17">
         <v>1540.0</v>
       </c>
-      <c r="C9" s="16"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="16">
-        <v>1530.0</v>
-      </c>
-      <c r="C10" s="16"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="s">
+      <c r="C13" s="17"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="17">
+        <v>1540.0</v>
+      </c>
+      <c r="C14" s="17"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B15" s="17">
         <v>1520.0</v>
       </c>
-      <c r="C11" s="16"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="16">
-        <v>1510.0</v>
-      </c>
-      <c r="C12" s="16"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="s">
+      <c r="C15" s="17"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B16" s="17">
         <v>1500.0</v>
       </c>
-      <c r="C13" s="16"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="16">
-        <v>1490.0</v>
-      </c>
-      <c r="C14" s="16"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="16">
-        <v>1480.0</v>
-      </c>
-      <c r="C15" s="16"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="s">
+      <c r="C16" s="17"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="17">
+        <v>1410.0</v>
+      </c>
+      <c r="C17" s="17"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B18" s="17">
         <v>1400.0</v>
       </c>
-      <c r="C16" s="16"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="s">
+      <c r="C18" s="17"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B19" s="17">
         <v>1400.0</v>
       </c>
-      <c r="C17" s="16"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B18" s="16">
-        <v>1360.0</v>
-      </c>
-      <c r="C18" s="16"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="s">
+      <c r="C19" s="17"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="17">
+        <v>1400.0</v>
+      </c>
+      <c r="C20" s="17"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="16">
-        <v>1350.0</v>
-      </c>
-      <c r="C19" s="16"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="s">
+      <c r="B21" s="17">
+        <v>1400.0</v>
+      </c>
+      <c r="C21" s="17"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="17">
+        <v>1390.0</v>
+      </c>
+      <c r="C22" s="18"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B23" s="19">
         <v>1340.0</v>
       </c>
-      <c r="C20" s="16"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="16">
-        <v>1300.0</v>
-      </c>
-      <c r="C21" s="16"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="16">
-        <v>1290.0</v>
-      </c>
-      <c r="C22" s="17"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="18">
-        <v>1130.0</v>
-      </c>
-      <c r="C23" s="16"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="7" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="17"/>
-      <c r="B24" s="16"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="17"/>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B25" s="20">
+      <c r="A25" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" s="21">
         <f>SUM(B2:B23)</f>
-        <v>32600</v>
+        <v>34580</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="B26" s="20">
+      <c r="A26" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" s="21">
         <f>ROUND(B25/22,0)</f>
-        <v>1482</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19"/>
-      <c r="B27" s="21"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="22"/>
     </row>
     <row r="28">
-      <c r="A28" s="19"/>
-      <c r="B28" s="22"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="23"/>
     </row>
     <row r="29">
-      <c r="A29" s="16"/>
+      <c r="A29" s="17"/>
     </row>
     <row r="30">
-      <c r="A30" s="16"/>
+      <c r="A30" s="17"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -7054,760 +7125,808 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23">
+      <c r="A1" s="24">
         <v>46207.0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="17">
+      <c r="C1" s="18">
         <v>1.0</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>131</v>
+      <c r="D1" s="18" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23">
+      <c r="A2" s="24">
         <v>46209.0</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="18">
         <v>1.0</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>132</v>
+      <c r="D2" s="18" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23">
+      <c r="A3" s="24">
         <v>46209.0</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="18">
         <v>1.0</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>132</v>
+      <c r="D3" s="18" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23">
+      <c r="A4" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="18">
         <v>1.0</v>
       </c>
-      <c r="D4" s="17" t="s">
-        <v>133</v>
+      <c r="D4" s="18" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23">
+      <c r="A5" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <v>1.0</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>133</v>
+      <c r="D5" s="18" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23">
+      <c r="A6" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="18">
         <v>1.0</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24">
+        <v>46214.0</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24">
+        <v>46217.0</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24">
+        <v>46218.0</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D19" s="18" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="23">
-        <v>46214.0</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="17">
+    <row r="20">
+      <c r="A20" s="24">
+        <v>46218.0</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="18">
         <v>1.0</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23">
-        <v>46214.0</v>
-      </c>
-      <c r="B8" s="17" t="s">
+      <c r="D20" s="18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24">
+        <v>46218.0</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C21" s="18">
         <v>1.0</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23">
-        <v>46214.0</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="17">
+      <c r="D21" s="18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24">
+        <v>46222.0</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="18">
         <v>1.0</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23">
-        <v>46214.0</v>
-      </c>
-      <c r="B10" s="17" t="s">
+      <c r="D22" s="18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24">
+        <v>46222.0</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24">
+        <v>46222.0</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24">
+        <v>46222.0</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24">
+        <v>46222.0</v>
+      </c>
+      <c r="B26" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C26" s="18">
         <v>1.0</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23">
-        <v>46214.0</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="17">
+      <c r="D26" s="18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24">
+        <v>46223.0</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="18">
         <v>1.0</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23">
-        <v>46214.0</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23">
-        <v>46214.0</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23">
-        <v>46214.0</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23">
-        <v>46214.0</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23">
-        <v>46214.0</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23">
-        <v>46214.0</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23">
-        <v>46217.0</v>
-      </c>
-      <c r="B18" s="17" t="s">
+      <c r="D27" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C18" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23">
-        <v>46218.0</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23">
-        <v>46218.0</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="23">
-        <v>46218.0</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="23"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="23"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
     </row>
     <row r="28">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
     </row>
     <row r="29">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
     </row>
     <row r="30">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
     </row>
     <row r="31">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
     </row>
     <row r="32">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
     </row>
     <row r="33">
-      <c r="A33" s="16"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
     </row>
     <row r="34">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
     </row>
     <row r="35">
-      <c r="A35" s="16"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
     </row>
     <row r="36">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
     </row>
     <row r="37">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
     </row>
     <row r="38">
-      <c r="A38" s="16"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
     </row>
     <row r="39">
-      <c r="A39" s="16"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
     </row>
     <row r="40">
-      <c r="A40" s="16"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
     </row>
     <row r="41">
-      <c r="A41" s="16"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
     </row>
     <row r="42">
-      <c r="A42" s="16"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
     </row>
     <row r="43">
-      <c r="A43" s="16"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
     </row>
     <row r="44">
-      <c r="A44" s="16"/>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
     </row>
     <row r="45">
-      <c r="A45" s="16"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
     </row>
     <row r="46">
-      <c r="A46" s="16"/>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
     </row>
     <row r="47">
-      <c r="A47" s="16"/>
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
     </row>
     <row r="48">
-      <c r="A48" s="16"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
     </row>
     <row r="49">
-      <c r="A49" s="16"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
     </row>
     <row r="50">
-      <c r="A50" s="16"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
     </row>
     <row r="51">
-      <c r="A51" s="16"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
     </row>
     <row r="52">
-      <c r="A52" s="16"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
     </row>
     <row r="53">
-      <c r="A53" s="16"/>
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
     </row>
     <row r="54">
-      <c r="A54" s="16"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
     </row>
     <row r="55">
-      <c r="A55" s="16"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
     </row>
     <row r="56">
-      <c r="A56" s="16"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
     </row>
     <row r="57">
-      <c r="A57" s="16"/>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
+      <c r="A57" s="17"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
     </row>
     <row r="58">
-      <c r="A58" s="16"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
+      <c r="A58" s="17"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
     </row>
     <row r="59">
-      <c r="A59" s="16"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
     </row>
     <row r="60">
-      <c r="A60" s="16"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
     </row>
     <row r="61">
-      <c r="A61" s="16"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
     </row>
     <row r="62">
-      <c r="A62" s="16"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
     </row>
     <row r="63">
-      <c r="A63" s="16"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
     </row>
     <row r="64">
-      <c r="A64" s="16"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
     </row>
     <row r="65">
-      <c r="A65" s="16"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
+      <c r="A65" s="17"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
     </row>
     <row r="66">
-      <c r="A66" s="16"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
     </row>
     <row r="67">
-      <c r="A67" s="16"/>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
     </row>
     <row r="68">
-      <c r="A68" s="16"/>
-      <c r="B68" s="16"/>
-      <c r="C68" s="16"/>
-      <c r="D68" s="16"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
     </row>
     <row r="69">
-      <c r="A69" s="16"/>
-      <c r="B69" s="16"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="16"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
     </row>
     <row r="70">
-      <c r="A70" s="16"/>
-      <c r="B70" s="16"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="16"/>
+      <c r="A70" s="17"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
     </row>
     <row r="71">
-      <c r="A71" s="16"/>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
     </row>
     <row r="72">
-      <c r="A72" s="16"/>
-      <c r="B72" s="16"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
+      <c r="A72" s="17"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
     </row>
     <row r="73">
-      <c r="A73" s="16"/>
-      <c r="B73" s="16"/>
-      <c r="C73" s="16"/>
-      <c r="D73" s="16"/>
+      <c r="A73" s="17"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="17"/>
     </row>
     <row r="74">
-      <c r="A74" s="16"/>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="16"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
     </row>
     <row r="75">
-      <c r="A75" s="16"/>
-      <c r="B75" s="16"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
     </row>
     <row r="76">
-      <c r="A76" s="16"/>
-      <c r="B76" s="16"/>
-      <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17"/>
     </row>
     <row r="77">
-      <c r="A77" s="16"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
+      <c r="A77" s="17"/>
+      <c r="B77" s="17"/>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
     </row>
     <row r="78">
-      <c r="A78" s="16"/>
-      <c r="B78" s="16"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
+      <c r="A78" s="17"/>
+      <c r="B78" s="17"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
     </row>
     <row r="79">
-      <c r="A79" s="16"/>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
+      <c r="A79" s="17"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
     </row>
     <row r="80">
-      <c r="A80" s="16"/>
-      <c r="B80" s="16"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
     </row>
     <row r="81">
-      <c r="A81" s="16"/>
-      <c r="B81" s="16"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
+      <c r="A81" s="17"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
     </row>
     <row r="82">
-      <c r="A82" s="16"/>
-      <c r="B82" s="16"/>
-      <c r="C82" s="16"/>
-      <c r="D82" s="16"/>
+      <c r="A82" s="17"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="17"/>
     </row>
     <row r="83">
-      <c r="A83" s="16"/>
-      <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
+      <c r="A83" s="17"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
     </row>
     <row r="84">
-      <c r="A84" s="16"/>
-      <c r="B84" s="16"/>
-      <c r="C84" s="16"/>
-      <c r="D84" s="16"/>
+      <c r="A84" s="17"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
     </row>
     <row r="85">
-      <c r="A85" s="16"/>
-      <c r="B85" s="16"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="16"/>
+      <c r="A85" s="17"/>
+      <c r="B85" s="17"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="17"/>
     </row>
     <row r="86">
-      <c r="A86" s="16"/>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="16"/>
+      <c r="A86" s="17"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="17"/>
     </row>
     <row r="87">
-      <c r="A87" s="16"/>
-      <c r="B87" s="16"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="16"/>
+      <c r="A87" s="17"/>
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="17"/>
     </row>
     <row r="88">
-      <c r="A88" s="16"/>
-      <c r="B88" s="16"/>
-      <c r="C88" s="16"/>
-      <c r="D88" s="16"/>
+      <c r="A88" s="17"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="17"/>
     </row>
     <row r="89">
-      <c r="A89" s="16"/>
-      <c r="B89" s="16"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="16"/>
+      <c r="A89" s="17"/>
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
     </row>
     <row r="90">
-      <c r="A90" s="16"/>
-      <c r="B90" s="16"/>
-      <c r="C90" s="16"/>
-      <c r="D90" s="16"/>
+      <c r="A90" s="17"/>
+      <c r="B90" s="17"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="17"/>
     </row>
     <row r="91">
-      <c r="A91" s="16"/>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="16"/>
+      <c r="A91" s="17"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="17"/>
     </row>
     <row r="92">
-      <c r="A92" s="16"/>
-      <c r="B92" s="16"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="16"/>
+      <c r="A92" s="17"/>
+      <c r="B92" s="17"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17"/>
     </row>
     <row r="93">
-      <c r="A93" s="16"/>
-      <c r="B93" s="16"/>
-      <c r="C93" s="16"/>
-      <c r="D93" s="16"/>
+      <c r="A93" s="17"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17"/>
     </row>
     <row r="94">
-      <c r="A94" s="16"/>
-      <c r="B94" s="16"/>
-      <c r="C94" s="16"/>
-      <c r="D94" s="16"/>
+      <c r="A94" s="17"/>
+      <c r="B94" s="17"/>
+      <c r="C94" s="17"/>
+      <c r="D94" s="17"/>
     </row>
     <row r="95">
-      <c r="A95" s="16"/>
-      <c r="B95" s="16"/>
-      <c r="C95" s="16"/>
-      <c r="D95" s="16"/>
+      <c r="A95" s="17"/>
+      <c r="B95" s="17"/>
+      <c r="C95" s="17"/>
+      <c r="D95" s="17"/>
     </row>
     <row r="96">
-      <c r="A96" s="16"/>
-      <c r="B96" s="16"/>
-      <c r="C96" s="16"/>
-      <c r="D96" s="16"/>
+      <c r="A96" s="17"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="17"/>
     </row>
     <row r="97">
-      <c r="A97" s="16"/>
-      <c r="B97" s="16"/>
-      <c r="C97" s="16"/>
-      <c r="D97" s="16"/>
+      <c r="A97" s="17"/>
+      <c r="B97" s="17"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="17"/>
     </row>
     <row r="98">
-      <c r="A98" s="16"/>
-      <c r="B98" s="16"/>
-      <c r="C98" s="16"/>
-      <c r="D98" s="16"/>
+      <c r="A98" s="17"/>
+      <c r="B98" s="17"/>
+      <c r="C98" s="17"/>
+      <c r="D98" s="17"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/wc.xlsx
+++ b/wc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="141">
   <si>
     <t>Thái Bình</t>
   </si>
@@ -1774,7 +1774,21 @@
     </r>
   </si>
   <si>
-    <t>Tây Ban Nha - Argentina</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Tây Ban Nha - </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Argentina</t>
+    </r>
   </si>
   <si>
     <t>Vua đóng góp</t>
@@ -1977,11 +1991,11 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -2235,39 +2249,39 @@
       </c>
       <c r="D1" s="1">
         <f t="shared" si="1"/>
-        <v>1410</v>
+        <v>1510</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F1" s="1">
         <f t="shared" si="1"/>
-        <v>1850</v>
+        <v>0</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" si="1"/>
-        <v>1540</v>
+        <v>1640</v>
       </c>
       <c r="H1" s="1">
         <f t="shared" si="1"/>
-        <v>1390</v>
+        <v>1290</v>
       </c>
       <c r="I1" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="J1" s="1">
         <f t="shared" si="1"/>
-        <v>1580</v>
+        <v>1680</v>
       </c>
       <c r="K1" s="1">
         <f t="shared" si="1"/>
-        <v>1520</v>
+        <v>1620</v>
       </c>
       <c r="L1" s="1">
         <f t="shared" si="1"/>
-        <v>1670</v>
+        <v>1770</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" si="1"/>
@@ -2275,15 +2289,15 @@
       </c>
       <c r="N1" s="1">
         <f t="shared" si="1"/>
-        <v>1580</v>
+        <v>1680</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" si="1"/>
-        <v>1560</v>
+        <v>1660</v>
       </c>
       <c r="P1" s="1">
         <f t="shared" si="1"/>
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" si="1"/>
@@ -2291,11 +2305,11 @@
       </c>
       <c r="R1" s="1">
         <f t="shared" si="1"/>
-        <v>1560</v>
+        <v>1760</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" si="1"/>
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="T1" s="1">
         <f t="shared" si="1"/>
@@ -2307,11 +2321,11 @@
       </c>
       <c r="V1" s="1">
         <f t="shared" si="1"/>
-        <v>1660</v>
+        <v>1760</v>
       </c>
       <c r="W1" s="1">
         <f t="shared" si="1"/>
-        <v>1650</v>
+        <v>1750</v>
       </c>
       <c r="X1" s="2">
         <f>COUNTIF(X3:X130,"&gt;0")</f>
@@ -6836,9 +6850,57 @@
       <c r="A106" s="6" t="s">
         <v>126</v>
       </c>
+      <c r="D106" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="E106" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="F106" s="14">
+        <v>-1850.0</v>
+      </c>
+      <c r="G106" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="H106" s="13">
+        <v>-100.0</v>
+      </c>
+      <c r="I106" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="J106" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="K106" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="L106" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="N106" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="O106" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="P106" s="13">
+        <v>-100.0</v>
+      </c>
+      <c r="R106" s="12">
+        <v>200.0</v>
+      </c>
+      <c r="S106" s="12">
+        <v>200.0</v>
+      </c>
+      <c r="V106" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="W106" s="7">
+        <v>100.0</v>
+      </c>
       <c r="X106" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-550</v>
       </c>
     </row>
     <row r="107">
@@ -6882,194 +6944,257 @@
       <c r="B2" s="17">
         <v>2260.0</v>
       </c>
-      <c r="C2" s="17"/>
+      <c r="C2" s="17">
+        <f t="shared" ref="C2:C22" si="1">B2-1000</f>
+        <v>1260</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B3" s="17">
-        <v>1850.0</v>
-      </c>
-      <c r="C3" s="17"/>
+        <v>1770.0</v>
+      </c>
+      <c r="C3" s="17">
+        <f t="shared" si="1"/>
+        <v>770</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="17">
-        <v>1700.0</v>
-      </c>
-      <c r="C4" s="17"/>
+        <v>1760.0</v>
+      </c>
+      <c r="C4" s="17">
+        <f t="shared" si="1"/>
+        <v>760</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B5" s="17">
-        <v>1670.0</v>
-      </c>
-      <c r="C5" s="17"/>
+        <v>1760.0</v>
+      </c>
+      <c r="C5" s="17">
+        <f t="shared" si="1"/>
+        <v>760</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B6" s="17">
-        <v>1670.0</v>
-      </c>
-      <c r="C6" s="17"/>
+        <v>1750.0</v>
+      </c>
+      <c r="C6" s="17">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B7" s="17">
-        <v>1660.0</v>
-      </c>
-      <c r="C7" s="17"/>
+        <v>1680.0</v>
+      </c>
+      <c r="C7" s="17">
+        <f t="shared" si="1"/>
+        <v>680</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B8" s="17">
-        <v>1650.0</v>
-      </c>
-      <c r="C8" s="17"/>
+        <v>1680.0</v>
+      </c>
+      <c r="C8" s="17">
+        <f t="shared" si="1"/>
+        <v>680</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B9" s="17">
-        <v>1580.0</v>
-      </c>
-      <c r="C9" s="17"/>
+        <v>1670.0</v>
+      </c>
+      <c r="C9" s="17">
+        <f t="shared" si="1"/>
+        <v>670</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="17">
-        <v>1580.0</v>
-      </c>
-      <c r="C10" s="17"/>
+        <v>1660.0</v>
+      </c>
+      <c r="C10" s="17">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B11" s="17">
-        <v>1560.0</v>
-      </c>
-      <c r="C11" s="17"/>
+        <v>1640.0</v>
+      </c>
+      <c r="C11" s="17">
+        <f t="shared" si="1"/>
+        <v>640</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B12" s="17">
-        <v>1560.0</v>
-      </c>
-      <c r="C12" s="17"/>
+        <v>1620.0</v>
+      </c>
+      <c r="C12" s="17">
+        <f t="shared" si="1"/>
+        <v>620</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B13" s="17">
-        <v>1540.0</v>
-      </c>
-      <c r="C13" s="17"/>
+        <v>1600.0</v>
+      </c>
+      <c r="C13" s="17">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="17">
-        <v>1540.0</v>
-      </c>
-      <c r="C14" s="17"/>
+        <v>1600.0</v>
+      </c>
+      <c r="C14" s="17">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B15" s="17">
-        <v>1520.0</v>
-      </c>
-      <c r="C15" s="17"/>
+        <v>1540.0</v>
+      </c>
+      <c r="C15" s="17">
+        <f t="shared" si="1"/>
+        <v>540</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B16" s="17">
-        <v>1500.0</v>
-      </c>
-      <c r="C16" s="17"/>
+        <v>1510.0</v>
+      </c>
+      <c r="C16" s="17">
+        <f t="shared" si="1"/>
+        <v>510</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" s="17">
-        <v>1410.0</v>
-      </c>
-      <c r="C17" s="17"/>
+        <v>1500.0</v>
+      </c>
+      <c r="C17" s="17">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B18" s="17">
-        <v>1400.0</v>
-      </c>
-      <c r="C18" s="17"/>
+        <v>1500.0</v>
+      </c>
+      <c r="C18" s="17">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B19" s="17">
-        <v>1400.0</v>
-      </c>
-      <c r="C19" s="17"/>
+        <v>1500.0</v>
+      </c>
+      <c r="C19" s="17">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B20" s="17">
         <v>1400.0</v>
       </c>
-      <c r="C20" s="17"/>
+      <c r="C20" s="17">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B21" s="17">
-        <v>1400.0</v>
-      </c>
-      <c r="C21" s="17"/>
+        <v>1340.0</v>
+      </c>
+      <c r="C21" s="17">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="17">
-        <v>1390.0</v>
-      </c>
-      <c r="C22" s="18"/>
+        <v>1290.0</v>
+      </c>
+      <c r="C22" s="17">
+        <f t="shared" si="1"/>
+        <v>290</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="19">
-        <v>1340.0</v>
+        <v>4</v>
+      </c>
+      <c r="B23" s="18">
+        <v>0.0</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="7" t="s">
@@ -7077,7 +7202,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="17"/>
     </row>
     <row r="25">
@@ -7086,7 +7211,11 @@
       </c>
       <c r="B25" s="21">
         <f>SUM(B2:B23)</f>
-        <v>34580</v>
+        <v>34030</v>
+      </c>
+      <c r="C25" s="2">
+        <f>sum(C2:C23)</f>
+        <v>13030</v>
       </c>
     </row>
     <row r="26">
@@ -7094,8 +7223,12 @@
         <v>131</v>
       </c>
       <c r="B26" s="21">
-        <f>ROUND(B25/22,0)</f>
-        <v>1572</v>
+        <f>ROUND(B25/21,0)</f>
+        <v>1620</v>
+      </c>
+      <c r="C26" s="2">
+        <f>C25/22</f>
+        <v>592.2727273</v>
       </c>
     </row>
     <row r="27">
@@ -7128,13 +7261,13 @@
       <c r="A1" s="24">
         <v>46207.0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="18">
+      <c r="C1" s="19">
         <v>1.0</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>132</v>
       </c>
     </row>
@@ -7142,13 +7275,13 @@
       <c r="A2" s="24">
         <v>46209.0</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="19">
         <v>1.0</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>133</v>
       </c>
     </row>
@@ -7156,13 +7289,13 @@
       <c r="A3" s="24">
         <v>46209.0</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="19">
         <v>1.0</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>133</v>
       </c>
     </row>
@@ -7170,13 +7303,13 @@
       <c r="A4" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="19">
         <v>1.0</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>134</v>
       </c>
     </row>
@@ -7184,13 +7317,13 @@
       <c r="A5" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <v>1.0</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>134</v>
       </c>
     </row>
@@ -7198,13 +7331,13 @@
       <c r="A6" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <v>1.0</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>135</v>
       </c>
     </row>
@@ -7212,13 +7345,13 @@
       <c r="A7" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <v>1.0</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>136</v>
       </c>
     </row>
@@ -7226,13 +7359,13 @@
       <c r="A8" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <v>1.0</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -7240,13 +7373,13 @@
       <c r="A9" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <v>1.0</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -7254,13 +7387,13 @@
       <c r="A10" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <v>1.0</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -7268,13 +7401,13 @@
       <c r="A11" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="19">
         <v>1.0</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -7282,13 +7415,13 @@
       <c r="A12" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <v>1.0</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -7296,13 +7429,13 @@
       <c r="A13" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="19">
         <v>1.0</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -7310,13 +7443,13 @@
       <c r="A14" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="19">
         <v>1.0</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -7324,13 +7457,13 @@
       <c r="A15" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="19">
         <v>1.0</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -7338,13 +7471,13 @@
       <c r="A16" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="19">
         <v>1.0</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -7352,13 +7485,13 @@
       <c r="A17" s="24">
         <v>46214.0</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="19">
         <v>1.0</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -7366,13 +7499,13 @@
       <c r="A18" s="24">
         <v>46217.0</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="19">
         <v>1.0</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>139</v>
       </c>
     </row>
@@ -7380,13 +7513,13 @@
       <c r="A19" s="24">
         <v>46218.0</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="19">
         <v>1.0</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="19" t="s">
         <v>134</v>
       </c>
     </row>
@@ -7394,13 +7527,13 @@
       <c r="A20" s="24">
         <v>46218.0</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="19">
         <v>1.0</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>134</v>
       </c>
     </row>
@@ -7408,13 +7541,13 @@
       <c r="A21" s="24">
         <v>46218.0</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="19">
         <v>1.0</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>134</v>
       </c>
     </row>
@@ -7422,13 +7555,13 @@
       <c r="A22" s="24">
         <v>46222.0</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="19">
         <v>1.0</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>140</v>
       </c>
     </row>
@@ -7436,13 +7569,13 @@
       <c r="A23" s="24">
         <v>46222.0</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="19">
         <v>1.0</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="19" t="s">
         <v>140</v>
       </c>
     </row>
@@ -7450,13 +7583,13 @@
       <c r="A24" s="24">
         <v>46222.0</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="19">
         <v>1.0</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="19" t="s">
         <v>140</v>
       </c>
     </row>
@@ -7464,13 +7597,13 @@
       <c r="A25" s="24">
         <v>46222.0</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="19">
         <v>1.0</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="19" t="s">
         <v>140</v>
       </c>
     </row>
@@ -7478,13 +7611,13 @@
       <c r="A26" s="24">
         <v>46222.0</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="19">
         <v>1.0</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="19" t="s">
         <v>140</v>
       </c>
     </row>
@@ -7492,33 +7625,57 @@
       <c r="A27" s="24">
         <v>46223.0</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="19">
         <v>1.0</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="19" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
+      <c r="A28" s="24">
+        <v>46223.0</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
+      <c r="A29" s="24">
+        <v>46223.0</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
+      <c r="A30" s="24">
+        <v>46223.0</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="17"/>
